--- a/worklog/カード明細_仕訳別集計_202512-202608.xlsx
+++ b/worklog/カード明細_仕訳別集計_202512-202608.xlsx
@@ -15,7 +15,7 @@
     <sheet name="経費削減提案" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">全明細!$A$1:$H$975</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">全明細!$A$1:$H$1068</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4488" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4910" uniqueCount="589">
   <si>
     <t xml:space="preserve">カード</t>
   </si>
@@ -4266,39 +4266,196 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">明細未添付分</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:ANA 5/11</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">支払明細の</t>
+    <t xml:space="preserve">ルミネ荻窪</t>
+  </si>
+  <si>
+    <t xml:space="preserve">東京協同タクシー</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">自治体</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">JMMS(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">券売機</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">自治体窓口</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日本再生酒場 中野店</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">*USEN</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">イートラベライフライトチケット</t>
+  </si>
+  <si>
+    <t xml:space="preserve">タリーズコーヒー新宿小滝橋通り</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月分</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">叙々苑 新宿歌舞伎町店</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">高額・コース契約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">オフィスコム本店</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(BtoB)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">オフィス家具</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PayPal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">決済</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">さかなの目玉</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Square</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">決済</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">店舗名不明・要確認</t>
+  </si>
+  <si>
+    <t xml:space="preserve">肉賊カウぼーず</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">大衆酒場 春田屋 練馬</t>
     </r>
     <r>
       <rPr>
@@ -4315,55 +4472,174 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">ページ目</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">不明・要確認</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PDF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未添付。合計</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">7,404,159</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円との差額</t>
+      <t xml:space="preserve">号店</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">カフェラリー新宿店</t>
+  </si>
+  <si>
+    <t xml:space="preserve">京鼎樓 新宿住友ビル店</t>
+  </si>
+  <si>
+    <t xml:space="preserve">陳家私菜 丸の内店</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ワッツ野方北原店</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円ショップ</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ファミリーマート</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">グリル大那古や 豊田上郷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上り</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">きしめん平川 豊田上郷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上り</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">前月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">STOPOVER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">と同額・要確認</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上島珈琲店 諏訪湖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">下り店</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">アティックルーム中野</t>
+  </si>
+  <si>
+    <t xml:space="preserve">東京電力</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AmazonPay</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">提携サイト</t>
     </r>
   </si>
   <si>
@@ -4579,15 +4855,49 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2026/8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">支払分</t>
+      <t xml:space="preserve">2026/9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">支払分 ※</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">支払分は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8/10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時点の未確定明細</t>
     </r>
     <r>
       <rPr>
@@ -4610,6 +4920,9 @@
   </si>
   <si>
     <t xml:space="preserve">構成比</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不明・要確認</t>
   </si>
   <si>
     <r>
@@ -4756,83 +5069,83 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">※ ANA 2026/5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">支払分のうち</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1,350,511</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円は明細</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PDF2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ページ目未添付のため内訳不明</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">全明細シート最終付近参照</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。</t>
+      <t xml:space="preserve">※ ANA 2026/9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">支払予定分</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(5,542,246</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円・利用日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/7/16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8/8)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026/8/10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時点の未確定明細を含む。</t>
     </r>
   </si>
   <si>
@@ -6317,6 +6630,40 @@
       </rPr>
       <t xml:space="preserve">円</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+2026/4/15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">137,060</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円のコース決済あり。継続要否を確認</t>
+    </r>
   </si>
   <si>
     <r>
@@ -8648,7 +8995,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">44,254</t>
+      <t xml:space="preserve">90,452</t>
     </r>
     <r>
       <rPr>
@@ -8682,17 +9029,136 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">0.8%)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">カード還元率が手数料率を上回るか確認。下回る場合はダイレクト納付</t>
+      <t xml:space="preserve">0.8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。例</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: 7/22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は納税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5,112,700</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円に手数料</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">42,198</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">カード還元率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">マイル・ポイント価値</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">が手数料率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を上回るか確認。下回る場合はダイレクト納付</t>
     </r>
     <r>
       <rPr>
@@ -9530,7 +9996,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H975"/>
+  <dimension ref="A1:H1068"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
@@ -34660,27 +35126,2452 @@
         <v>170</v>
       </c>
       <c r="C975" s="3" t="n">
-        <v>46142</v>
+        <v>46120</v>
       </c>
       <c r="D975" s="2" t="str">
         <f aca="false">TEXT(C975,"YYYY-MM")</f>
         <v>2026-04</v>
       </c>
       <c r="E975" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F975" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G975" s="5" t="n">
+        <v>1380</v>
+      </c>
+      <c r="H975" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="976" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A976" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B976" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C976" s="3" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D976" s="2" t="str">
+        <f aca="false">TEXT(C976,"YYYY-MM")</f>
+        <v>2026-04</v>
+      </c>
+      <c r="E976" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="F975" s="4" t="s">
+      <c r="F976" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G976" s="5" t="n">
+        <v>1977</v>
+      </c>
+      <c r="H976" s="2"/>
+    </row>
+    <row r="977" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A977" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B977" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C977" s="3" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D977" s="2" t="str">
+        <f aca="false">TEXT(C977,"YYYY-MM")</f>
+        <v>2026-04</v>
+      </c>
+      <c r="E977" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F977" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G977" s="5" t="n">
+        <v>2480</v>
+      </c>
+      <c r="H977" s="2"/>
+    </row>
+    <row r="978" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A978" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B978" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C978" s="3" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D978" s="2" t="str">
+        <f aca="false">TEXT(C978,"YYYY-MM")</f>
+        <v>2026-04</v>
+      </c>
+      <c r="E978" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="G975" s="5" t="n">
-        <v>1350511</v>
-      </c>
-      <c r="H975" s="2" t="s">
+      <c r="F978" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G978" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="H978" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="979" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A979" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B979" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C979" s="3" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D979" s="2" t="str">
+        <f aca="false">TEXT(C979,"YYYY-MM")</f>
+        <v>2026-04</v>
+      </c>
+      <c r="E979" s="4" t="s">
         <v>441</v>
       </c>
+      <c r="F979" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G979" s="5" t="n">
+        <v>800</v>
+      </c>
+      <c r="H979" s="4" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="980" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A980" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B980" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C980" s="3" t="n">
+        <v>46121</v>
+      </c>
+      <c r="D980" s="2" t="str">
+        <f aca="false">TEXT(C980,"YYYY-MM")</f>
+        <v>2026-04</v>
+      </c>
+      <c r="E980" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F980" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G980" s="5" t="n">
+        <v>1550</v>
+      </c>
+      <c r="H980" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="981" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A981" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B981" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C981" s="3" t="n">
+        <v>46122</v>
+      </c>
+      <c r="D981" s="2" t="str">
+        <f aca="false">TEXT(C981,"YYYY-MM")</f>
+        <v>2026-04</v>
+      </c>
+      <c r="E981" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F981" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="G981" s="5" t="n">
+        <v>36784</v>
+      </c>
+      <c r="H981" s="4" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="982" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A982" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B982" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C982" s="3" t="n">
+        <v>46122</v>
+      </c>
+      <c r="D982" s="2" t="str">
+        <f aca="false">TEXT(C982,"YYYY-MM")</f>
+        <v>2026-04</v>
+      </c>
+      <c r="E982" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F982" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G982" s="5" t="n">
+        <v>465367</v>
+      </c>
+      <c r="H982" s="2"/>
+    </row>
+    <row r="983" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A983" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B983" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C983" s="3" t="n">
+        <v>46122</v>
+      </c>
+      <c r="D983" s="2" t="str">
+        <f aca="false">TEXT(C983,"YYYY-MM")</f>
+        <v>2026-04</v>
+      </c>
+      <c r="E983" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F983" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G983" s="5" t="n">
+        <v>488200</v>
+      </c>
+      <c r="H983" s="2"/>
+    </row>
+    <row r="984" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A984" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B984" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C984" s="3" t="n">
+        <v>46122</v>
+      </c>
+      <c r="D984" s="2" t="str">
+        <f aca="false">TEXT(C984,"YYYY-MM")</f>
+        <v>2026-04</v>
+      </c>
+      <c r="E984" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F984" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G984" s="5" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H984" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="985" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A985" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B985" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C985" s="3" t="n">
+        <v>46122</v>
+      </c>
+      <c r="D985" s="2" t="str">
+        <f aca="false">TEXT(C985,"YYYY-MM")</f>
+        <v>2026-04</v>
+      </c>
+      <c r="E985" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="F985" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G985" s="5" t="n">
+        <v>6754</v>
+      </c>
+      <c r="H985" s="2"/>
+    </row>
+    <row r="986" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A986" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B986" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C986" s="3" t="n">
+        <v>46122</v>
+      </c>
+      <c r="D986" s="2" t="str">
+        <f aca="false">TEXT(C986,"YYYY-MM")</f>
+        <v>2026-04</v>
+      </c>
+      <c r="E986" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F986" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G986" s="5" t="n">
+        <v>1380</v>
+      </c>
+      <c r="H986" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="987" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A987" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B987" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C987" s="3" t="n">
+        <v>46123</v>
+      </c>
+      <c r="D987" s="2" t="str">
+        <f aca="false">TEXT(C987,"YYYY-MM")</f>
+        <v>2026-04</v>
+      </c>
+      <c r="E987" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F987" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G987" s="5" t="n">
+        <v>1580</v>
+      </c>
+      <c r="H987" s="2"/>
+    </row>
+    <row r="988" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A988" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B988" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C988" s="3" t="n">
+        <v>46124</v>
+      </c>
+      <c r="D988" s="2" t="str">
+        <f aca="false">TEXT(C988,"YYYY-MM")</f>
+        <v>2026-04</v>
+      </c>
+      <c r="E988" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F988" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G988" s="5" t="n">
+        <v>15825</v>
+      </c>
+      <c r="H988" s="2"/>
+    </row>
+    <row r="989" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A989" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B989" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C989" s="3" t="n">
+        <v>46124</v>
+      </c>
+      <c r="D989" s="2" t="str">
+        <f aca="false">TEXT(C989,"YYYY-MM")</f>
+        <v>2026-04</v>
+      </c>
+      <c r="E989" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="F989" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G989" s="5" t="n">
+        <v>16500</v>
+      </c>
+      <c r="H989" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="990" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A990" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B990" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C990" s="3" t="n">
+        <v>46125</v>
+      </c>
+      <c r="D990" s="2" t="str">
+        <f aca="false">TEXT(C990,"YYYY-MM")</f>
+        <v>2026-04</v>
+      </c>
+      <c r="E990" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="F990" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G990" s="5" t="n">
+        <v>450</v>
+      </c>
+      <c r="H990" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="991" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A991" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B991" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C991" s="3" t="n">
+        <v>46125</v>
+      </c>
+      <c r="D991" s="2" t="str">
+        <f aca="false">TEXT(C991,"YYYY-MM")</f>
+        <v>2026-04</v>
+      </c>
+      <c r="E991" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="F991" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G991" s="5" t="n">
+        <v>96895</v>
+      </c>
+      <c r="H991" s="4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="992" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A992" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B992" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C992" s="3" t="n">
+        <v>46125</v>
+      </c>
+      <c r="D992" s="2" t="str">
+        <f aca="false">TEXT(C992,"YYYY-MM")</f>
+        <v>2026-04</v>
+      </c>
+      <c r="E992" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="F992" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G992" s="5" t="n">
+        <v>450</v>
+      </c>
+      <c r="H992" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="993" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A993" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B993" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C993" s="3" t="n">
+        <v>46125</v>
+      </c>
+      <c r="D993" s="2" t="str">
+        <f aca="false">TEXT(C993,"YYYY-MM")</f>
+        <v>2026-04</v>
+      </c>
+      <c r="E993" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F993" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G993" s="5" t="n">
+        <v>1980</v>
+      </c>
+      <c r="H993" s="2"/>
+    </row>
+    <row r="994" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A994" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B994" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C994" s="3" t="n">
+        <v>46126</v>
+      </c>
+      <c r="D994" s="2" t="str">
+        <f aca="false">TEXT(C994,"YYYY-MM")</f>
+        <v>2026-04</v>
+      </c>
+      <c r="E994" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="F994" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G994" s="5" t="n">
+        <v>2736</v>
+      </c>
+      <c r="H994" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="995" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A995" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B995" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C995" s="3" t="n">
+        <v>46126</v>
+      </c>
+      <c r="D995" s="2" t="str">
+        <f aca="false">TEXT(C995,"YYYY-MM")</f>
+        <v>2026-04</v>
+      </c>
+      <c r="E995" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="F995" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G995" s="5" t="n">
+        <v>3200</v>
+      </c>
+      <c r="H995" s="2"/>
+    </row>
+    <row r="996" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A996" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B996" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C996" s="3" t="n">
+        <v>46126</v>
+      </c>
+      <c r="D996" s="2" t="str">
+        <f aca="false">TEXT(C996,"YYYY-MM")</f>
+        <v>2026-04</v>
+      </c>
+      <c r="E996" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F996" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G996" s="5" t="n">
+        <v>1700</v>
+      </c>
+      <c r="H996" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="997" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A997" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B997" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C997" s="3" t="n">
+        <v>46127</v>
+      </c>
+      <c r="D997" s="2" t="str">
+        <f aca="false">TEXT(C997,"YYYY-MM")</f>
+        <v>2026-04</v>
+      </c>
+      <c r="E997" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F997" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="G997" s="5" t="n">
+        <v>137060</v>
+      </c>
+      <c r="H997" s="4" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="998" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A998" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B998" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C998" s="3" t="n">
+        <v>46127</v>
+      </c>
+      <c r="D998" s="2" t="str">
+        <f aca="false">TEXT(C998,"YYYY-MM")</f>
+        <v>2026-04</v>
+      </c>
+      <c r="E998" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F998" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G998" s="5" t="n">
+        <v>4800</v>
+      </c>
+      <c r="H998" s="2"/>
+    </row>
+    <row r="999" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A999" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B999" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C999" s="3" t="n">
+        <v>46127</v>
+      </c>
+      <c r="D999" s="2" t="str">
+        <f aca="false">TEXT(C999,"YYYY-MM")</f>
+        <v>2026-04</v>
+      </c>
+      <c r="E999" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="F999" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G999" s="5" t="n">
+        <v>55963</v>
+      </c>
+      <c r="H999" s="4" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="1000" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1000" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1000" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1000" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="D1000" s="2" t="str">
+        <f aca="false">TEXT(C1000,"YYYY-MM")</f>
+        <v>2026-08</v>
+      </c>
+      <c r="E1000" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F1000" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1000" s="5" t="n">
+        <v>3580</v>
+      </c>
+      <c r="H1000" s="2"/>
+    </row>
+    <row r="1001" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1001" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1001" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1001" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="D1001" s="2" t="str">
+        <f aca="false">TEXT(C1001,"YYYY-MM")</f>
+        <v>2026-08</v>
+      </c>
+      <c r="E1001" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="F1001" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1001" s="5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="H1001" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="1002" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1002" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1002" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1002" s="3" t="n">
+        <v>46241</v>
+      </c>
+      <c r="D1002" s="2" t="str">
+        <f aca="false">TEXT(C1002,"YYYY-MM")</f>
+        <v>2026-08</v>
+      </c>
+      <c r="E1002" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="F1002" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1002" s="5" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H1002" s="2"/>
+    </row>
+    <row r="1003" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1003" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1003" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1003" s="3" t="n">
+        <v>46241</v>
+      </c>
+      <c r="D1003" s="2" t="str">
+        <f aca="false">TEXT(C1003,"YYYY-MM")</f>
+        <v>2026-08</v>
+      </c>
+      <c r="E1003" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="F1003" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1003" s="5" t="n">
+        <v>13650</v>
+      </c>
+      <c r="H1003" s="2"/>
+    </row>
+    <row r="1004" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1004" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1004" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1004" s="3" t="n">
+        <v>46240</v>
+      </c>
+      <c r="D1004" s="2" t="str">
+        <f aca="false">TEXT(C1004,"YYYY-MM")</f>
+        <v>2026-08</v>
+      </c>
+      <c r="E1004" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="F1004" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1004" s="5" t="n">
+        <v>4880</v>
+      </c>
+      <c r="H1004" s="4" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="1005" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1005" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1005" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1005" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D1005" s="2" t="str">
+        <f aca="false">TEXT(C1005,"YYYY-MM")</f>
+        <v>2026-08</v>
+      </c>
+      <c r="E1005" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="F1005" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1005" s="5" t="n">
+        <v>19378</v>
+      </c>
+      <c r="H1005" s="2"/>
+    </row>
+    <row r="1006" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1006" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1006" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1006" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D1006" s="2" t="str">
+        <f aca="false">TEXT(C1006,"YYYY-MM")</f>
+        <v>2026-08</v>
+      </c>
+      <c r="E1006" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1006" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1006" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H1006" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1007" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1007" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1007" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1007" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="D1007" s="2" t="str">
+        <f aca="false">TEXT(C1007,"YYYY-MM")</f>
+        <v>2026-08</v>
+      </c>
+      <c r="E1007" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="F1007" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1007" s="5" t="n">
+        <v>1900</v>
+      </c>
+      <c r="H1007" s="2"/>
+    </row>
+    <row r="1008" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1008" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1008" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1008" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="D1008" s="2" t="str">
+        <f aca="false">TEXT(C1008,"YYYY-MM")</f>
+        <v>2026-08</v>
+      </c>
+      <c r="E1008" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F1008" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1008" s="5" t="n">
+        <v>1958</v>
+      </c>
+      <c r="H1008" s="2"/>
+    </row>
+    <row r="1009" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1009" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1009" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1009" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="D1009" s="2" t="str">
+        <f aca="false">TEXT(C1009,"YYYY-MM")</f>
+        <v>2026-08</v>
+      </c>
+      <c r="E1009" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="F1009" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1009" s="5" t="n">
+        <v>1431</v>
+      </c>
+      <c r="H1009" s="4" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="1010" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1010" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1010" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1010" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="D1010" s="2" t="str">
+        <f aca="false">TEXT(C1010,"YYYY-MM")</f>
+        <v>2026-08</v>
+      </c>
+      <c r="E1010" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F1010" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1010" s="5" t="n">
+        <v>2980</v>
+      </c>
+      <c r="H1010" s="2"/>
+    </row>
+    <row r="1011" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1011" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1011" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1011" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="D1011" s="2" t="str">
+        <f aca="false">TEXT(C1011,"YYYY-MM")</f>
+        <v>2026-08</v>
+      </c>
+      <c r="E1011" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="F1011" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1011" s="5" t="n">
+        <v>800</v>
+      </c>
+      <c r="H1011" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1012" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1012" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1012" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1012" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="D1012" s="2" t="str">
+        <f aca="false">TEXT(C1012,"YYYY-MM")</f>
+        <v>2026-08</v>
+      </c>
+      <c r="E1012" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="F1012" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1012" s="5" t="n">
+        <v>2200</v>
+      </c>
+      <c r="H1012" s="2"/>
+    </row>
+    <row r="1013" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1013" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1013" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1013" s="3" t="n">
+        <v>46236</v>
+      </c>
+      <c r="D1013" s="2" t="str">
+        <f aca="false">TEXT(C1013,"YYYY-MM")</f>
+        <v>2026-08</v>
+      </c>
+      <c r="E1013" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="F1013" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1013" s="5" t="n">
+        <v>8508</v>
+      </c>
+      <c r="H1013" s="2"/>
+    </row>
+    <row r="1014" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1014" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1014" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1014" s="3" t="n">
+        <v>46236</v>
+      </c>
+      <c r="D1014" s="2" t="str">
+        <f aca="false">TEXT(C1014,"YYYY-MM")</f>
+        <v>2026-08</v>
+      </c>
+      <c r="E1014" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="F1014" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1014" s="5" t="n">
+        <v>1630</v>
+      </c>
+      <c r="H1014" s="2"/>
+    </row>
+    <row r="1015" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1015" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1015" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1015" s="3" t="n">
+        <v>46236</v>
+      </c>
+      <c r="D1015" s="2" t="str">
+        <f aca="false">TEXT(C1015,"YYYY-MM")</f>
+        <v>2026-08</v>
+      </c>
+      <c r="E1015" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="F1015" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1015" s="5" t="n">
+        <v>1700</v>
+      </c>
+      <c r="H1015" s="4" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="1016" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1016" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1016" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1016" s="3" t="n">
+        <v>46236</v>
+      </c>
+      <c r="D1016" s="2" t="str">
+        <f aca="false">TEXT(C1016,"YYYY-MM")</f>
+        <v>2026-08</v>
+      </c>
+      <c r="E1016" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="F1016" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1016" s="5" t="n">
+        <v>2968</v>
+      </c>
+      <c r="H1016" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="1017" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1017" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1017" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1017" s="3" t="n">
+        <v>46236</v>
+      </c>
+      <c r="D1017" s="2" t="str">
+        <f aca="false">TEXT(C1017,"YYYY-MM")</f>
+        <v>2026-08</v>
+      </c>
+      <c r="E1017" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="F1017" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1017" s="5" t="n">
+        <v>6050</v>
+      </c>
+      <c r="H1017" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="1018" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1018" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1018" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1018" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="D1018" s="2" t="str">
+        <f aca="false">TEXT(C1018,"YYYY-MM")</f>
+        <v>2026-08</v>
+      </c>
+      <c r="E1018" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="F1018" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G1018" s="5" t="n">
+        <v>33000</v>
+      </c>
+      <c r="H1018" s="2"/>
+    </row>
+    <row r="1019" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1019" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1019" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1019" s="3" t="n">
+        <v>46234</v>
+      </c>
+      <c r="D1019" s="2" t="str">
+        <f aca="false">TEXT(C1019,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1019" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1019" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1019" s="5" t="n">
+        <v>1380</v>
+      </c>
+      <c r="H1019" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1020" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1020" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1020" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1020" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="D1020" s="2" t="str">
+        <f aca="false">TEXT(C1020,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1020" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="F1020" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1020" s="5" t="n">
+        <v>344</v>
+      </c>
+      <c r="H1020" s="2"/>
+    </row>
+    <row r="1021" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1021" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1021" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1021" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="D1021" s="2" t="str">
+        <f aca="false">TEXT(C1021,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1021" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F1021" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1021" s="5" t="n">
+        <v>3254</v>
+      </c>
+      <c r="H1021" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1022" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1022" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1022" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1022" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="D1022" s="2" t="str">
+        <f aca="false">TEXT(C1022,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1022" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F1022" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1022" s="5" t="n">
+        <v>2084</v>
+      </c>
+      <c r="H1022" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1023" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1023" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1023" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1023" s="3" t="n">
+        <v>46233</v>
+      </c>
+      <c r="D1023" s="2" t="str">
+        <f aca="false">TEXT(C1023,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1023" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="F1023" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1023" s="5" t="n">
+        <v>21660</v>
+      </c>
+      <c r="H1023" s="4" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="1024" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1024" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1024" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1024" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="D1024" s="2" t="str">
+        <f aca="false">TEXT(C1024,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1024" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1024" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1024" s="5" t="n">
+        <v>510</v>
+      </c>
+      <c r="H1024" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1025" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1025" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1025" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1025" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="D1025" s="2" t="str">
+        <f aca="false">TEXT(C1025,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1025" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="F1025" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1025" s="5" t="n">
+        <v>1990</v>
+      </c>
+      <c r="H1025" s="2"/>
+    </row>
+    <row r="1026" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1026" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1026" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1026" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="D1026" s="2" t="str">
+        <f aca="false">TEXT(C1026,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1026" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="F1026" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1026" s="5" t="n">
+        <v>1848</v>
+      </c>
+      <c r="H1026" s="2"/>
+    </row>
+    <row r="1027" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1027" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1027" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1027" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="D1027" s="2" t="str">
+        <f aca="false">TEXT(C1027,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1027" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="F1027" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1027" s="5" t="n">
+        <v>1090</v>
+      </c>
+      <c r="H1027" s="2"/>
+    </row>
+    <row r="1028" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1028" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1028" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1028" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="D1028" s="2" t="str">
+        <f aca="false">TEXT(C1028,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1028" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="F1028" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1028" s="5" t="n">
+        <v>33000</v>
+      </c>
+      <c r="H1028" s="4" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="1029" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1029" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1029" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1029" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="D1029" s="2" t="str">
+        <f aca="false">TEXT(C1029,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1029" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="F1029" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1029" s="5" t="n">
+        <v>22000</v>
+      </c>
+      <c r="H1029" s="4" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="1030" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1030" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1030" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1030" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="D1030" s="2" t="str">
+        <f aca="false">TEXT(C1030,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1030" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="F1030" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1030" s="5" t="n">
+        <v>7049</v>
+      </c>
+      <c r="H1030" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1031" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1031" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1031" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1031" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="D1031" s="2" t="str">
+        <f aca="false">TEXT(C1031,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1031" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="F1031" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1031" s="5" t="n">
+        <v>38610</v>
+      </c>
+      <c r="H1031" s="4" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="1032" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1032" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1032" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1032" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="D1032" s="2" t="str">
+        <f aca="false">TEXT(C1032,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1032" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="F1032" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1032" s="5" t="n">
+        <v>860</v>
+      </c>
+      <c r="H1032" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1033" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1033" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1033" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1033" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="D1033" s="2" t="str">
+        <f aca="false">TEXT(C1033,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1033" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F1033" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1033" s="5" t="n">
+        <v>6745</v>
+      </c>
+      <c r="H1033" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1034" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1034" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1034" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1034" s="3" t="n">
+        <v>46232</v>
+      </c>
+      <c r="D1034" s="2" t="str">
+        <f aca="false">TEXT(C1034,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1034" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F1034" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1034" s="5" t="n">
+        <v>18000</v>
+      </c>
+      <c r="H1034" s="2"/>
+    </row>
+    <row r="1035" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1035" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1035" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1035" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="D1035" s="2" t="str">
+        <f aca="false">TEXT(C1035,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1035" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F1035" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1035" s="5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H1035" s="4" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="1036" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1036" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1036" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1036" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="D1036" s="2" t="str">
+        <f aca="false">TEXT(C1036,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1036" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1036" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1036" s="5" t="n">
+        <v>1480</v>
+      </c>
+      <c r="H1036" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1037" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1037" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1037" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1037" s="3" t="n">
+        <v>46230</v>
+      </c>
+      <c r="D1037" s="2" t="str">
+        <f aca="false">TEXT(C1037,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1037" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="F1037" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1037" s="5" t="n">
+        <v>1850</v>
+      </c>
+      <c r="H1037" s="2"/>
+    </row>
+    <row r="1038" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1038" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1038" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1038" s="3" t="n">
+        <v>46230</v>
+      </c>
+      <c r="D1038" s="2" t="str">
+        <f aca="false">TEXT(C1038,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1038" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1038" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1038" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H1038" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1039" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1039" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1039" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1039" s="3" t="n">
+        <v>46229</v>
+      </c>
+      <c r="D1039" s="2" t="str">
+        <f aca="false">TEXT(C1039,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1039" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F1039" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1039" s="5" t="n">
+        <v>2200</v>
+      </c>
+      <c r="H1039" s="2"/>
+    </row>
+    <row r="1040" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1040" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1040" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1040" s="3" t="n">
+        <v>46229</v>
+      </c>
+      <c r="D1040" s="2" t="str">
+        <f aca="false">TEXT(C1040,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1040" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1040" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1040" s="5" t="n">
+        <v>1380</v>
+      </c>
+      <c r="H1040" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1041" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1041" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1041" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1041" s="3" t="n">
+        <v>46228</v>
+      </c>
+      <c r="D1041" s="2" t="str">
+        <f aca="false">TEXT(C1041,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1041" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F1041" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1041" s="5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H1041" s="2"/>
+    </row>
+    <row r="1042" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1042" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1042" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1042" s="3" t="n">
+        <v>46227</v>
+      </c>
+      <c r="D1042" s="2" t="str">
+        <f aca="false">TEXT(C1042,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1042" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F1042" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1042" s="5" t="n">
+        <v>6300</v>
+      </c>
+      <c r="H1042" s="2"/>
+    </row>
+    <row r="1043" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1043" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1043" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1043" s="3" t="n">
+        <v>46227</v>
+      </c>
+      <c r="D1043" s="2" t="str">
+        <f aca="false">TEXT(C1043,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1043" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="F1043" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1043" s="5" t="n">
+        <v>2079</v>
+      </c>
+      <c r="H1043" s="2"/>
+    </row>
+    <row r="1044" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1044" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1044" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1044" s="3" t="n">
+        <v>46227</v>
+      </c>
+      <c r="D1044" s="2" t="str">
+        <f aca="false">TEXT(C1044,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1044" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1044" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1044" s="5" t="n">
+        <v>760</v>
+      </c>
+      <c r="H1044" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1045" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1045" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1045" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1045" s="3" t="n">
+        <v>46226</v>
+      </c>
+      <c r="D1045" s="2" t="str">
+        <f aca="false">TEXT(C1045,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1045" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1045" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1045" s="5" t="n">
+        <v>1080</v>
+      </c>
+      <c r="H1045" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1046" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1046" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1046" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1046" s="3" t="n">
+        <v>46226</v>
+      </c>
+      <c r="D1046" s="2" t="str">
+        <f aca="false">TEXT(C1046,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1046" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="F1046" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1046" s="5" t="n">
+        <v>1229</v>
+      </c>
+      <c r="H1046" s="2"/>
+    </row>
+    <row r="1047" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1047" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1047" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1047" s="3" t="n">
+        <v>46226</v>
+      </c>
+      <c r="D1047" s="2" t="str">
+        <f aca="false">TEXT(C1047,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1047" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F1047" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1047" s="5" t="n">
+        <v>7037</v>
+      </c>
+      <c r="H1047" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1048" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1048" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1048" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1048" s="3" t="n">
+        <v>46226</v>
+      </c>
+      <c r="D1048" s="2" t="str">
+        <f aca="false">TEXT(C1048,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1048" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1048" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1048" s="5" t="n">
+        <v>780</v>
+      </c>
+      <c r="H1048" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1049" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1049" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1049" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1049" s="3" t="n">
+        <v>46226</v>
+      </c>
+      <c r="D1049" s="2" t="str">
+        <f aca="false">TEXT(C1049,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1049" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1049" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1049" s="5" t="n">
+        <v>1460</v>
+      </c>
+      <c r="H1049" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1050" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1050" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1050" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1050" s="3" t="n">
+        <v>46225</v>
+      </c>
+      <c r="D1050" s="2" t="str">
+        <f aca="false">TEXT(C1050,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1050" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1050" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1050" s="5" t="n">
+        <v>5112700</v>
+      </c>
+      <c r="H1050" s="4" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="1051" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1051" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1051" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1051" s="3" t="n">
+        <v>46225</v>
+      </c>
+      <c r="D1051" s="2" t="str">
+        <f aca="false">TEXT(C1051,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1051" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1051" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1051" s="5" t="n">
+        <v>42198</v>
+      </c>
+      <c r="H1051" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="1052" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1052" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1052" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1052" s="3" t="n">
+        <v>46225</v>
+      </c>
+      <c r="D1052" s="2" t="str">
+        <f aca="false">TEXT(C1052,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1052" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F1052" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1052" s="5" t="n">
+        <v>8400</v>
+      </c>
+      <c r="H1052" s="2"/>
+    </row>
+    <row r="1053" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1053" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1053" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1053" s="3" t="n">
+        <v>46225</v>
+      </c>
+      <c r="D1053" s="2" t="str">
+        <f aca="false">TEXT(C1053,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1053" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1053" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1053" s="5" t="n">
+        <v>1460</v>
+      </c>
+      <c r="H1053" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1054" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1054" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1054" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1054" s="3" t="n">
+        <v>46225</v>
+      </c>
+      <c r="D1054" s="2" t="str">
+        <f aca="false">TEXT(C1054,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1054" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="F1054" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1054" s="5" t="n">
+        <v>550</v>
+      </c>
+      <c r="H1054" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1055" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1055" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1055" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1055" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="D1055" s="2" t="str">
+        <f aca="false">TEXT(C1055,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1055" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="F1055" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1055" s="5" t="n">
+        <v>2398</v>
+      </c>
+      <c r="H1055" s="2"/>
+    </row>
+    <row r="1056" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1056" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1056" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1056" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="D1056" s="2" t="str">
+        <f aca="false">TEXT(C1056,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1056" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F1056" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1056" s="5" t="n">
+        <v>3610</v>
+      </c>
+      <c r="H1056" s="2"/>
+    </row>
+    <row r="1057" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1057" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1057" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1057" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="D1057" s="2" t="str">
+        <f aca="false">TEXT(C1057,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1057" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1057" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1057" s="5" t="n">
+        <v>3850</v>
+      </c>
+      <c r="H1057" s="2"/>
+    </row>
+    <row r="1058" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1058" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1058" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1058" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="D1058" s="2" t="str">
+        <f aca="false">TEXT(C1058,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1058" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="F1058" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1058" s="5" t="n">
+        <v>615</v>
+      </c>
+      <c r="H1058" s="2"/>
+    </row>
+    <row r="1059" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1059" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1059" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1059" s="3" t="n">
+        <v>46223</v>
+      </c>
+      <c r="D1059" s="2" t="str">
+        <f aca="false">TEXT(C1059,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1059" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1059" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1059" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H1059" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1060" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1060" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1060" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1060" s="3" t="n">
+        <v>46223</v>
+      </c>
+      <c r="D1060" s="2" t="str">
+        <f aca="false">TEXT(C1060,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1060" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="F1060" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1060" s="5" t="n">
+        <v>800</v>
+      </c>
+      <c r="H1060" s="2"/>
+    </row>
+    <row r="1061" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1061" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1061" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1061" s="3" t="n">
+        <v>46222</v>
+      </c>
+      <c r="D1061" s="2" t="str">
+        <f aca="false">TEXT(C1061,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1061" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F1061" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1061" s="5" t="n">
+        <v>1540</v>
+      </c>
+      <c r="H1061" s="2"/>
+    </row>
+    <row r="1062" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1062" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1062" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1062" s="3" t="n">
+        <v>46222</v>
+      </c>
+      <c r="D1062" s="2" t="str">
+        <f aca="false">TEXT(C1062,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1062" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F1062" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1062" s="5" t="n">
+        <v>2750</v>
+      </c>
+      <c r="H1062" s="2"/>
+    </row>
+    <row r="1063" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1063" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1063" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1063" s="3" t="n">
+        <v>46222</v>
+      </c>
+      <c r="D1063" s="2" t="str">
+        <f aca="false">TEXT(C1063,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1063" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1063" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1063" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H1063" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1064" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1064" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1064" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1064" s="3" t="n">
+        <v>46221</v>
+      </c>
+      <c r="D1064" s="2" t="str">
+        <f aca="false">TEXT(C1064,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1064" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="F1064" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1064" s="5" t="n">
+        <v>1330</v>
+      </c>
+      <c r="H1064" s="2"/>
+    </row>
+    <row r="1065" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1065" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1065" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1065" s="3" t="n">
+        <v>46220</v>
+      </c>
+      <c r="D1065" s="2" t="str">
+        <f aca="false">TEXT(C1065,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1065" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F1065" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1065" s="5" t="n">
+        <v>1112</v>
+      </c>
+      <c r="H1065" s="2"/>
+    </row>
+    <row r="1066" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1066" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1066" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1066" s="3" t="n">
+        <v>46220</v>
+      </c>
+      <c r="D1066" s="2" t="str">
+        <f aca="false">TEXT(C1066,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1066" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="F1066" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1066" s="5" t="n">
+        <v>14861</v>
+      </c>
+      <c r="H1066" s="4" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="1067" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1067" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1067" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1067" s="3" t="n">
+        <v>46220</v>
+      </c>
+      <c r="D1067" s="2" t="str">
+        <f aca="false">TEXT(C1067,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1067" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1067" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1067" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H1067" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1068" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1068" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1068" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1068" s="3" t="n">
+        <v>46219</v>
+      </c>
+      <c r="D1068" s="2" t="str">
+        <f aca="false">TEXT(C1068,"YYYY-MM")</f>
+        <v>2026-07</v>
+      </c>
+      <c r="E1068" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="F1068" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1068" s="5" t="n">
+        <v>36500</v>
+      </c>
+      <c r="H1068" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H975"/>
+  <autoFilter ref="A1:H1068"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -34706,12 +37597,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>442</v>
+        <v>471</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>443</v>
+        <v>472</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34719,10 +37610,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>444</v>
+        <v>473</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>445</v>
+        <v>474</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>9</v>
@@ -34752,10 +37643,10 @@
         <v>244</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>446</v>
+        <v>475</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>447</v>
+        <v>476</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34763,56 +37654,56 @@
         <v>62</v>
       </c>
       <c r="B5" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A5,全明細!$D$2:$D$975,B$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A5,全明細!$D$2:$D$1068,B$4)</f>
         <v>0</v>
       </c>
       <c r="C5" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A5,全明細!$D$2:$D$975,C$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A5,全明細!$D$2:$D$1068,C$4)</f>
         <v>1353341</v>
       </c>
       <c r="D5" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A5,全明細!$D$2:$D$975,D$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A5,全明細!$D$2:$D$1068,D$4)</f>
         <v>492200</v>
       </c>
       <c r="E5" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A5,全明細!$D$2:$D$975,E$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A5,全明細!$D$2:$D$1068,E$4)</f>
         <v>943741</v>
       </c>
       <c r="F5" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A5,全明細!$D$2:$D$975,F$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A5,全明細!$D$2:$D$1068,F$4)</f>
         <v>878054</v>
       </c>
       <c r="G5" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A5,全明細!$D$2:$D$975,G$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A5,全明細!$D$2:$D$1068,G$4)</f>
         <v>9010409</v>
       </c>
       <c r="H5" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A5,全明細!$D$2:$D$975,H$4)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A5,全明細!$D$2:$D$1068,H$4)</f>
+        <v>957567</v>
       </c>
       <c r="I5" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A5,全明細!$D$2:$D$975,I$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A5,全明細!$D$2:$D$1068,I$4)</f>
         <v>3473800</v>
       </c>
       <c r="J5" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A5,全明細!$D$2:$D$975,J$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A5,全明細!$D$2:$D$1068,J$4)</f>
         <v>902641</v>
       </c>
       <c r="K5" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A5,全明細!$D$2:$D$975,K$4)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A5,全明細!$D$2:$D$1068,K$4)</f>
+        <v>5154898</v>
       </c>
       <c r="L5" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A5,全明細!$D$2:$D$975,L$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A5,全明細!$D$2:$D$1068,L$4)</f>
         <v>0</v>
       </c>
       <c r="M5" s="10" t="n">
         <f aca="false">SUM(B5:L5)</f>
-        <v>17054186</v>
+        <v>23166651</v>
       </c>
       <c r="N5" s="11" t="n">
         <f aca="false">IF(M$22=0,0,M5/M$22)</f>
-        <v>0.570507620127693</v>
+        <v>0.653774184005311</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34820,56 +37711,56 @@
         <v>58</v>
       </c>
       <c r="B6" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A6,全明細!$D$2:$D$975,B$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A6,全明細!$D$2:$D$1068,B$4)</f>
         <v>0</v>
       </c>
       <c r="C6" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A6,全明細!$D$2:$D$975,C$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A6,全明細!$D$2:$D$1068,C$4)</f>
         <v>214793</v>
       </c>
       <c r="D6" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A6,全明細!$D$2:$D$975,D$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A6,全明細!$D$2:$D$1068,D$4)</f>
         <v>277880</v>
       </c>
       <c r="E6" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A6,全明細!$D$2:$D$975,E$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A6,全明細!$D$2:$D$1068,E$4)</f>
         <v>278146</v>
       </c>
       <c r="F6" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A6,全明細!$D$2:$D$975,F$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A6,全明細!$D$2:$D$1068,F$4)</f>
         <v>205458</v>
       </c>
       <c r="G6" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A6,全明細!$D$2:$D$975,G$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A6,全明細!$D$2:$D$1068,G$4)</f>
         <v>163995</v>
       </c>
       <c r="H6" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A6,全明細!$D$2:$D$975,H$4)</f>
-        <v>131727</v>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A6,全明細!$D$2:$D$1068,H$4)</f>
+        <v>147552</v>
       </c>
       <c r="I6" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A6,全明細!$D$2:$D$975,I$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A6,全明細!$D$2:$D$1068,I$4)</f>
         <v>302309</v>
       </c>
       <c r="J6" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A6,全明細!$D$2:$D$975,J$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A6,全明細!$D$2:$D$1068,J$4)</f>
         <v>315123</v>
       </c>
       <c r="K6" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A6,全明細!$D$2:$D$975,K$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A6,全明細!$D$2:$D$1068,K$4)</f>
         <v>275240</v>
       </c>
       <c r="L6" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A6,全明細!$D$2:$D$975,L$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A6,全明細!$D$2:$D$1068,L$4)</f>
         <v>30000</v>
       </c>
       <c r="M6" s="10" t="n">
         <f aca="false">SUM(B6:L6)</f>
-        <v>2194671</v>
+        <v>2210496</v>
       </c>
       <c r="N6" s="11" t="n">
         <f aca="false">IF(M$22=0,0,M6/M$22)</f>
-        <v>0.0734175485815192</v>
+        <v>0.0623812746454808</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34877,56 +37768,56 @@
         <v>37</v>
       </c>
       <c r="B7" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A7,全明細!$D$2:$D$975,B$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A7,全明細!$D$2:$D$1068,B$4)</f>
         <v>0</v>
       </c>
       <c r="C7" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A7,全明細!$D$2:$D$975,C$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A7,全明細!$D$2:$D$1068,C$4)</f>
         <v>93333</v>
       </c>
       <c r="D7" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A7,全明細!$D$2:$D$975,D$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A7,全明細!$D$2:$D$1068,D$4)</f>
         <v>215342</v>
       </c>
       <c r="E7" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A7,全明細!$D$2:$D$975,E$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A7,全明細!$D$2:$D$1068,E$4)</f>
         <v>1366700</v>
       </c>
       <c r="F7" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A7,全明細!$D$2:$D$975,F$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A7,全明細!$D$2:$D$1068,F$4)</f>
         <v>932351</v>
       </c>
       <c r="G7" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A7,全明細!$D$2:$D$975,G$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A7,全明細!$D$2:$D$1068,G$4)</f>
         <v>761052</v>
       </c>
       <c r="H7" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A7,全明細!$D$2:$D$975,H$4)</f>
-        <v>249824</v>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A7,全明細!$D$2:$D$1068,H$4)</f>
+        <v>308267</v>
       </c>
       <c r="I7" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A7,全明細!$D$2:$D$975,I$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A7,全明細!$D$2:$D$1068,I$4)</f>
         <v>131502</v>
       </c>
       <c r="J7" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A7,全明細!$D$2:$D$975,J$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A7,全明細!$D$2:$D$1068,J$4)</f>
         <v>407649</v>
       </c>
       <c r="K7" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A7,全明細!$D$2:$D$975,K$4)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A7,全明細!$D$2:$D$1068,K$4)</f>
+        <v>80412</v>
       </c>
       <c r="L7" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A7,全明細!$D$2:$D$975,L$4)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A7,全明細!$D$2:$D$1068,L$4)</f>
+        <v>11486</v>
       </c>
       <c r="M7" s="10" t="n">
         <f aca="false">SUM(B7:L7)</f>
-        <v>4157753</v>
+        <v>4308094</v>
       </c>
       <c r="N7" s="11" t="n">
         <f aca="false">IF(M$22=0,0,M7/M$22)</f>
-        <v>0.139087832694494</v>
+        <v>0.121576512697851</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34934,56 +37825,56 @@
         <v>13</v>
       </c>
       <c r="B8" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A8,全明細!$D$2:$D$975,B$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A8,全明細!$D$2:$D$1068,B$4)</f>
         <v>4700</v>
       </c>
       <c r="C8" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A8,全明細!$D$2:$D$975,C$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A8,全明細!$D$2:$D$1068,C$4)</f>
         <v>148720</v>
       </c>
       <c r="D8" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A8,全明細!$D$2:$D$975,D$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A8,全明細!$D$2:$D$1068,D$4)</f>
         <v>77440</v>
       </c>
       <c r="E8" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A8,全明細!$D$2:$D$975,E$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A8,全明細!$D$2:$D$1068,E$4)</f>
         <v>31690</v>
       </c>
       <c r="F8" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A8,全明細!$D$2:$D$975,F$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A8,全明細!$D$2:$D$1068,F$4)</f>
         <v>66560</v>
       </c>
       <c r="G8" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A8,全明細!$D$2:$D$975,G$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A8,全明細!$D$2:$D$1068,G$4)</f>
         <v>114705</v>
       </c>
       <c r="H8" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A8,全明細!$D$2:$D$975,H$4)</f>
-        <v>129064</v>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A8,全明細!$D$2:$D$1068,H$4)</f>
+        <v>226659</v>
       </c>
       <c r="I8" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A8,全明細!$D$2:$D$975,I$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A8,全明細!$D$2:$D$1068,I$4)</f>
         <v>300004</v>
       </c>
       <c r="J8" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A8,全明細!$D$2:$D$975,J$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A8,全明細!$D$2:$D$1068,J$4)</f>
         <v>468600</v>
       </c>
       <c r="K8" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A8,全明細!$D$2:$D$975,K$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A8,全明細!$D$2:$D$1068,K$4)</f>
         <v>57281</v>
       </c>
       <c r="L8" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A8,全明細!$D$2:$D$975,L$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A8,全明細!$D$2:$D$1068,L$4)</f>
         <v>0</v>
       </c>
       <c r="M8" s="10" t="n">
         <f aca="false">SUM(B8:L8)</f>
-        <v>1398764</v>
+        <v>1496359</v>
       </c>
       <c r="N8" s="11" t="n">
         <f aca="false">IF(M$22=0,0,M8/M$22)</f>
-        <v>0.0467923547192632</v>
+        <v>0.0422279803931955</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34991,56 +37882,56 @@
         <v>17</v>
       </c>
       <c r="B9" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A9,全明細!$D$2:$D$975,B$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A9,全明細!$D$2:$D$1068,B$4)</f>
         <v>0</v>
       </c>
       <c r="C9" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A9,全明細!$D$2:$D$975,C$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A9,全明細!$D$2:$D$1068,C$4)</f>
         <v>13035</v>
       </c>
       <c r="D9" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A9,全明細!$D$2:$D$975,D$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A9,全明細!$D$2:$D$1068,D$4)</f>
         <v>10189</v>
       </c>
       <c r="E9" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A9,全明細!$D$2:$D$975,E$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A9,全明細!$D$2:$D$1068,E$4)</f>
         <v>32055</v>
       </c>
       <c r="F9" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A9,全明細!$D$2:$D$975,F$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A9,全明細!$D$2:$D$1068,F$4)</f>
         <v>15093</v>
       </c>
       <c r="G9" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A9,全明細!$D$2:$D$975,G$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A9,全明細!$D$2:$D$1068,G$4)</f>
         <v>329194</v>
       </c>
       <c r="H9" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A9,全明細!$D$2:$D$975,H$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A9,全明細!$D$2:$D$1068,H$4)</f>
         <v>9920</v>
       </c>
       <c r="I9" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A9,全明細!$D$2:$D$975,I$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A9,全明細!$D$2:$D$1068,I$4)</f>
         <v>27850</v>
       </c>
       <c r="J9" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A9,全明細!$D$2:$D$975,J$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A9,全明細!$D$2:$D$1068,J$4)</f>
         <v>294560</v>
       </c>
       <c r="K9" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A9,全明細!$D$2:$D$975,K$4)</f>
-        <v>3540</v>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A9,全明細!$D$2:$D$1068,K$4)</f>
+        <v>89979</v>
       </c>
       <c r="L9" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A9,全明細!$D$2:$D$975,L$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A9,全明細!$D$2:$D$1068,L$4)</f>
         <v>0</v>
       </c>
       <c r="M9" s="10" t="n">
         <f aca="false">SUM(B9:L9)</f>
-        <v>735436</v>
+        <v>821875</v>
       </c>
       <c r="N9" s="11" t="n">
         <f aca="false">IF(M$22=0,0,M9/M$22)</f>
-        <v>0.0246022790015443</v>
+        <v>0.0231937131301095</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35048,56 +37939,56 @@
         <v>22</v>
       </c>
       <c r="B10" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A10,全明細!$D$2:$D$975,B$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A10,全明細!$D$2:$D$1068,B$4)</f>
         <v>0</v>
       </c>
       <c r="C10" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A10,全明細!$D$2:$D$975,C$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A10,全明細!$D$2:$D$1068,C$4)</f>
         <v>65922</v>
       </c>
       <c r="D10" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A10,全明細!$D$2:$D$975,D$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A10,全明細!$D$2:$D$1068,D$4)</f>
         <v>82644</v>
       </c>
       <c r="E10" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A10,全明細!$D$2:$D$975,E$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A10,全明細!$D$2:$D$1068,E$4)</f>
         <v>59879</v>
       </c>
       <c r="F10" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A10,全明細!$D$2:$D$975,F$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A10,全明細!$D$2:$D$1068,F$4)</f>
         <v>79273</v>
       </c>
       <c r="G10" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A10,全明細!$D$2:$D$975,G$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A10,全明細!$D$2:$D$1068,G$4)</f>
         <v>114759</v>
       </c>
       <c r="H10" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A10,全明細!$D$2:$D$975,H$4)</f>
-        <v>93846</v>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A10,全明細!$D$2:$D$1068,H$4)</f>
+        <v>114270</v>
       </c>
       <c r="I10" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A10,全明細!$D$2:$D$975,I$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A10,全明細!$D$2:$D$1068,I$4)</f>
         <v>238677</v>
       </c>
       <c r="J10" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A10,全明細!$D$2:$D$975,J$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A10,全明細!$D$2:$D$1068,J$4)</f>
         <v>49888</v>
       </c>
       <c r="K10" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A10,全明細!$D$2:$D$975,K$4)</f>
-        <v>9689</v>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A10,全明細!$D$2:$D$1068,K$4)</f>
+        <v>32749</v>
       </c>
       <c r="L10" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A10,全明細!$D$2:$D$975,L$4)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A10,全明細!$D$2:$D$1068,L$4)</f>
+        <v>49066</v>
       </c>
       <c r="M10" s="10" t="n">
         <f aca="false">SUM(B10:L10)</f>
-        <v>794577</v>
+        <v>887127</v>
       </c>
       <c r="N10" s="11" t="n">
         <f aca="false">IF(M$22=0,0,M10/M$22)</f>
-        <v>0.0265807018451776</v>
+        <v>0.0250351563777638</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35105,47 +37996,47 @@
         <v>35</v>
       </c>
       <c r="B11" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A11,全明細!$D$2:$D$975,B$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A11,全明細!$D$2:$D$1068,B$4)</f>
         <v>0</v>
       </c>
       <c r="C11" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A11,全明細!$D$2:$D$975,C$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A11,全明細!$D$2:$D$1068,C$4)</f>
         <v>33900</v>
       </c>
       <c r="D11" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A11,全明細!$D$2:$D$975,D$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A11,全明細!$D$2:$D$1068,D$4)</f>
         <v>21028</v>
       </c>
       <c r="E11" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A11,全明細!$D$2:$D$975,E$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A11,全明細!$D$2:$D$1068,E$4)</f>
         <v>20278</v>
       </c>
       <c r="F11" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A11,全明細!$D$2:$D$975,F$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A11,全明細!$D$2:$D$1068,F$4)</f>
         <v>15780</v>
       </c>
       <c r="G11" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A11,全明細!$D$2:$D$975,G$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A11,全明細!$D$2:$D$1068,G$4)</f>
         <v>121050</v>
       </c>
       <c r="H11" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A11,全明細!$D$2:$D$975,H$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A11,全明細!$D$2:$D$1068,H$4)</f>
         <v>26613</v>
       </c>
       <c r="I11" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A11,全明細!$D$2:$D$975,I$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A11,全明細!$D$2:$D$1068,I$4)</f>
         <v>60181</v>
       </c>
       <c r="J11" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A11,全明細!$D$2:$D$975,J$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A11,全明細!$D$2:$D$1068,J$4)</f>
         <v>58125</v>
       </c>
       <c r="K11" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A11,全明細!$D$2:$D$975,K$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A11,全明細!$D$2:$D$1068,K$4)</f>
         <v>53999</v>
       </c>
       <c r="L11" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A11,全明細!$D$2:$D$975,L$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A11,全明細!$D$2:$D$1068,L$4)</f>
         <v>1580</v>
       </c>
       <c r="M11" s="10" t="n">
@@ -35154,7 +38045,7 @@
       </c>
       <c r="N11" s="11" t="n">
         <f aca="false">IF(M$22=0,0,M11/M$22)</f>
-        <v>0.0138003532130914</v>
+        <v>0.0116419105732826</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35162,56 +38053,56 @@
         <v>87</v>
       </c>
       <c r="B12" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A12,全明細!$D$2:$D$975,B$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A12,全明細!$D$2:$D$1068,B$4)</f>
         <v>0</v>
       </c>
       <c r="C12" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A12,全明細!$D$2:$D$975,C$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A12,全明細!$D$2:$D$1068,C$4)</f>
         <v>32780</v>
       </c>
       <c r="D12" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A12,全明細!$D$2:$D$975,D$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A12,全明細!$D$2:$D$1068,D$4)</f>
         <v>32780</v>
       </c>
       <c r="E12" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A12,全明細!$D$2:$D$975,E$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A12,全明細!$D$2:$D$1068,E$4)</f>
         <v>130680</v>
       </c>
       <c r="F12" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A12,全明細!$D$2:$D$975,F$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A12,全明細!$D$2:$D$1068,F$4)</f>
         <v>49280</v>
       </c>
       <c r="G12" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A12,全明細!$D$2:$D$975,G$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A12,全明細!$D$2:$D$1068,G$4)</f>
         <v>49280</v>
       </c>
       <c r="H12" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A12,全明細!$D$2:$D$975,H$4)</f>
-        <v>32780</v>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A12,全明細!$D$2:$D$1068,H$4)</f>
+        <v>49280</v>
       </c>
       <c r="I12" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A12,全明細!$D$2:$D$975,I$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A12,全明細!$D$2:$D$1068,I$4)</f>
         <v>49280</v>
       </c>
       <c r="J12" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A12,全明細!$D$2:$D$975,J$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A12,全明細!$D$2:$D$1068,J$4)</f>
         <v>52580</v>
       </c>
       <c r="K12" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A12,全明細!$D$2:$D$975,K$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A12,全明細!$D$2:$D$1068,K$4)</f>
         <v>3300</v>
       </c>
       <c r="L12" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A12,全明細!$D$2:$D$975,L$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A12,全明細!$D$2:$D$1068,L$4)</f>
         <v>0</v>
       </c>
       <c r="M12" s="10" t="n">
         <f aca="false">SUM(B12:L12)</f>
-        <v>432740</v>
+        <v>449240</v>
       </c>
       <c r="N12" s="11" t="n">
         <f aca="false">IF(M$22=0,0,M12/M$22)</f>
-        <v>0.0144762973462385</v>
+        <v>0.0126777717859412</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35219,56 +38110,56 @@
         <v>15</v>
       </c>
       <c r="B13" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A13,全明細!$D$2:$D$975,B$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A13,全明細!$D$2:$D$1068,B$4)</f>
         <v>12169</v>
       </c>
       <c r="C13" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A13,全明細!$D$2:$D$975,C$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A13,全明細!$D$2:$D$1068,C$4)</f>
         <v>20874</v>
       </c>
       <c r="D13" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A13,全明細!$D$2:$D$975,D$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A13,全明細!$D$2:$D$1068,D$4)</f>
         <v>20792</v>
       </c>
       <c r="E13" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A13,全明細!$D$2:$D$975,E$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A13,全明細!$D$2:$D$1068,E$4)</f>
         <v>28335</v>
       </c>
       <c r="F13" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A13,全明細!$D$2:$D$975,F$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A13,全明細!$D$2:$D$1068,F$4)</f>
         <v>21501</v>
       </c>
       <c r="G13" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A13,全明細!$D$2:$D$975,G$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A13,全明細!$D$2:$D$1068,G$4)</f>
         <v>17559</v>
       </c>
       <c r="H13" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A13,全明細!$D$2:$D$975,H$4)</f>
-        <v>13443</v>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A13,全明細!$D$2:$D$1068,H$4)</f>
+        <v>16179</v>
       </c>
       <c r="I13" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A13,全明細!$D$2:$D$975,I$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A13,全明細!$D$2:$D$1068,I$4)</f>
         <v>20798</v>
       </c>
       <c r="J13" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A13,全明細!$D$2:$D$975,J$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A13,全明細!$D$2:$D$1068,J$4)</f>
         <v>15782</v>
       </c>
       <c r="K13" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A13,全明細!$D$2:$D$975,K$4)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A13,全明細!$D$2:$D$1068,K$4)</f>
+        <v>1200</v>
       </c>
       <c r="L13" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A13,全明細!$D$2:$D$975,L$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A13,全明細!$D$2:$D$1068,L$4)</f>
         <v>0</v>
       </c>
       <c r="M13" s="10" t="n">
         <f aca="false">SUM(B13:L13)</f>
-        <v>171253</v>
+        <v>175189</v>
       </c>
       <c r="N13" s="11" t="n">
         <f aca="false">IF(M$22=0,0,M13/M$22)</f>
-        <v>0.00572886571482965</v>
+        <v>0.00494391897740016</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35276,56 +38167,56 @@
         <v>11</v>
       </c>
       <c r="B14" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A14,全明細!$D$2:$D$975,B$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A14,全明細!$D$2:$D$1068,B$4)</f>
         <v>2408</v>
       </c>
       <c r="C14" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A14,全明細!$D$2:$D$975,C$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A14,全明細!$D$2:$D$1068,C$4)</f>
         <v>6609</v>
       </c>
       <c r="D14" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A14,全明細!$D$2:$D$975,D$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A14,全明細!$D$2:$D$1068,D$4)</f>
         <v>2685</v>
       </c>
       <c r="E14" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A14,全明細!$D$2:$D$975,E$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A14,全明細!$D$2:$D$1068,E$4)</f>
         <v>2838</v>
       </c>
       <c r="F14" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A14,全明細!$D$2:$D$975,F$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A14,全明細!$D$2:$D$1068,F$4)</f>
         <v>6182</v>
       </c>
       <c r="G14" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A14,全明細!$D$2:$D$975,G$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A14,全明細!$D$2:$D$1068,G$4)</f>
         <v>9792</v>
       </c>
       <c r="H14" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A14,全明細!$D$2:$D$975,H$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A14,全明細!$D$2:$D$1068,H$4)</f>
         <v>9561</v>
       </c>
       <c r="I14" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A14,全明細!$D$2:$D$975,I$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A14,全明細!$D$2:$D$1068,I$4)</f>
         <v>15973</v>
       </c>
       <c r="J14" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A14,全明細!$D$2:$D$975,J$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A14,全明細!$D$2:$D$1068,J$4)</f>
         <v>13063</v>
       </c>
       <c r="K14" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A14,全明細!$D$2:$D$975,K$4)</f>
-        <v>12574</v>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A14,全明細!$D$2:$D$1068,K$4)</f>
+        <v>13189</v>
       </c>
       <c r="L14" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A14,全明細!$D$2:$D$975,L$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A14,全明細!$D$2:$D$1068,L$4)</f>
         <v>0</v>
       </c>
       <c r="M14" s="10" t="n">
         <f aca="false">SUM(B14:L14)</f>
-        <v>81685</v>
+        <v>82300</v>
       </c>
       <c r="N14" s="11" t="n">
         <f aca="false">IF(M$22=0,0,M14/M$22)</f>
-        <v>0.00273257925943406</v>
+        <v>0.00232254611785005</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35333,56 +38224,56 @@
         <v>173</v>
       </c>
       <c r="B15" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A15,全明細!$D$2:$D$975,B$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A15,全明細!$D$2:$D$1068,B$4)</f>
         <v>0</v>
       </c>
       <c r="C15" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A15,全明細!$D$2:$D$975,C$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A15,全明細!$D$2:$D$1068,C$4)</f>
         <v>0</v>
       </c>
       <c r="D15" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A15,全明細!$D$2:$D$975,D$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A15,全明細!$D$2:$D$1068,D$4)</f>
         <v>0</v>
       </c>
       <c r="E15" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A15,全明細!$D$2:$D$975,E$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A15,全明細!$D$2:$D$1068,E$4)</f>
         <v>0</v>
       </c>
       <c r="F15" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A15,全明細!$D$2:$D$975,F$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A15,全明細!$D$2:$D$1068,F$4)</f>
         <v>0</v>
       </c>
       <c r="G15" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A15,全明細!$D$2:$D$975,G$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A15,全明細!$D$2:$D$1068,G$4)</f>
         <v>0</v>
       </c>
       <c r="H15" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A15,全明細!$D$2:$D$975,H$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A15,全明細!$D$2:$D$1068,H$4)</f>
         <v>77000</v>
       </c>
       <c r="I15" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A15,全明細!$D$2:$D$975,I$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A15,全明細!$D$2:$D$1068,I$4)</f>
         <v>33000</v>
       </c>
       <c r="J15" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A15,全明細!$D$2:$D$975,J$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A15,全明細!$D$2:$D$1068,J$4)</f>
         <v>0</v>
       </c>
       <c r="K15" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A15,全明細!$D$2:$D$975,K$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A15,全明細!$D$2:$D$1068,K$4)</f>
         <v>8000</v>
       </c>
       <c r="L15" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A15,全明細!$D$2:$D$975,L$4)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A15,全明細!$D$2:$D$1068,L$4)</f>
+        <v>33000</v>
       </c>
       <c r="M15" s="10" t="n">
         <f aca="false">SUM(B15:L15)</f>
-        <v>118000</v>
+        <v>151000</v>
       </c>
       <c r="N15" s="11" t="n">
         <f aca="false">IF(M$22=0,0,M15/M$22)</f>
-        <v>0.00394741204154029</v>
+        <v>0.00426129360626195</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35390,56 +38281,56 @@
         <v>26</v>
       </c>
       <c r="B16" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A16,全明細!$D$2:$D$975,B$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A16,全明細!$D$2:$D$1068,B$4)</f>
         <v>0</v>
       </c>
       <c r="C16" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A16,全明細!$D$2:$D$975,C$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A16,全明細!$D$2:$D$1068,C$4)</f>
         <v>6760</v>
       </c>
       <c r="D16" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A16,全明細!$D$2:$D$975,D$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A16,全明細!$D$2:$D$1068,D$4)</f>
         <v>0</v>
       </c>
       <c r="E16" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A16,全明細!$D$2:$D$975,E$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A16,全明細!$D$2:$D$1068,E$4)</f>
         <v>7390</v>
       </c>
       <c r="F16" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A16,全明細!$D$2:$D$975,F$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A16,全明細!$D$2:$D$1068,F$4)</f>
         <v>5140</v>
       </c>
       <c r="G16" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A16,全明細!$D$2:$D$975,G$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A16,全明細!$D$2:$D$1068,G$4)</f>
         <v>4500</v>
       </c>
       <c r="H16" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A16,全明細!$D$2:$D$975,H$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A16,全明細!$D$2:$D$1068,H$4)</f>
         <v>1500</v>
       </c>
       <c r="I16" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A16,全明細!$D$2:$D$975,I$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A16,全明細!$D$2:$D$1068,I$4)</f>
         <v>0</v>
       </c>
       <c r="J16" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A16,全明細!$D$2:$D$975,J$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A16,全明細!$D$2:$D$1068,J$4)</f>
         <v>0</v>
       </c>
       <c r="K16" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A16,全明細!$D$2:$D$975,K$4)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A16,全明細!$D$2:$D$1068,K$4)</f>
+        <v>1500</v>
       </c>
       <c r="L16" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A16,全明細!$D$2:$D$975,L$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A16,全明細!$D$2:$D$1068,L$4)</f>
         <v>0</v>
       </c>
       <c r="M16" s="10" t="n">
         <f aca="false">SUM(B16:L16)</f>
-        <v>25290</v>
+        <v>26790</v>
       </c>
       <c r="N16" s="11" t="n">
         <f aca="false">IF(M$22=0,0,M16/M$22)</f>
-        <v>0.000846017377377576</v>
+        <v>0.000756026859018262</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35447,56 +38338,56 @@
         <v>137</v>
       </c>
       <c r="B17" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A17,全明細!$D$2:$D$975,B$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A17,全明細!$D$2:$D$1068,B$4)</f>
         <v>0</v>
       </c>
       <c r="C17" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A17,全明細!$D$2:$D$975,C$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A17,全明細!$D$2:$D$1068,C$4)</f>
         <v>0</v>
       </c>
       <c r="D17" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A17,全明細!$D$2:$D$975,D$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A17,全明細!$D$2:$D$1068,D$4)</f>
         <v>0</v>
       </c>
       <c r="E17" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A17,全明細!$D$2:$D$975,E$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A17,全明細!$D$2:$D$1068,E$4)</f>
         <v>15400</v>
       </c>
       <c r="F17" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A17,全明細!$D$2:$D$975,F$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A17,全明細!$D$2:$D$1068,F$4)</f>
         <v>69342</v>
       </c>
       <c r="G17" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A17,全明細!$D$2:$D$975,G$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A17,全明細!$D$2:$D$1068,G$4)</f>
         <v>60014</v>
       </c>
       <c r="H17" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A17,全明細!$D$2:$D$975,H$4)</f>
-        <v>10780</v>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A17,全明細!$D$2:$D$1068,H$4)</f>
+        <v>184624</v>
       </c>
       <c r="I17" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A17,全明細!$D$2:$D$975,I$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A17,全明細!$D$2:$D$1068,I$4)</f>
         <v>82984</v>
       </c>
       <c r="J17" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A17,全明細!$D$2:$D$975,J$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A17,全明細!$D$2:$D$1068,J$4)</f>
         <v>48325</v>
       </c>
       <c r="K17" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A17,全明細!$D$2:$D$975,K$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A17,全明細!$D$2:$D$1068,K$4)</f>
         <v>0</v>
       </c>
       <c r="L17" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A17,全明細!$D$2:$D$975,L$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A17,全明細!$D$2:$D$1068,L$4)</f>
         <v>0</v>
       </c>
       <c r="M17" s="10" t="n">
         <f aca="false">SUM(B17:L17)</f>
-        <v>286845</v>
+        <v>460689</v>
       </c>
       <c r="N17" s="11" t="n">
         <f aca="false">IF(M$22=0,0,M17/M$22)</f>
-        <v>0.00959572378860699</v>
+        <v>0.0130008681468557</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35504,56 +38395,56 @@
         <v>68</v>
       </c>
       <c r="B18" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A18,全明細!$D$2:$D$975,B$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A18,全明細!$D$2:$D$1068,B$4)</f>
         <v>0</v>
       </c>
       <c r="C18" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A18,全明細!$D$2:$D$975,C$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A18,全明細!$D$2:$D$1068,C$4)</f>
         <v>5005</v>
       </c>
       <c r="D18" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A18,全明細!$D$2:$D$975,D$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A18,全明細!$D$2:$D$1068,D$4)</f>
         <v>0</v>
       </c>
       <c r="E18" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A18,全明細!$D$2:$D$975,E$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A18,全明細!$D$2:$D$1068,E$4)</f>
         <v>0</v>
       </c>
       <c r="F18" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A18,全明細!$D$2:$D$975,F$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A18,全明細!$D$2:$D$1068,F$4)</f>
         <v>0</v>
       </c>
       <c r="G18" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A18,全明細!$D$2:$D$975,G$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A18,全明細!$D$2:$D$1068,G$4)</f>
         <v>10340</v>
       </c>
       <c r="H18" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A18,全明細!$D$2:$D$975,H$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A18,全明細!$D$2:$D$1068,H$4)</f>
         <v>6050</v>
       </c>
       <c r="I18" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A18,全明細!$D$2:$D$975,I$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A18,全明細!$D$2:$D$1068,I$4)</f>
         <v>13750</v>
       </c>
       <c r="J18" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A18,全明細!$D$2:$D$975,J$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A18,全明細!$D$2:$D$1068,J$4)</f>
         <v>6050</v>
       </c>
       <c r="K18" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A18,全明細!$D$2:$D$975,K$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A18,全明細!$D$2:$D$1068,K$4)</f>
         <v>0</v>
       </c>
       <c r="L18" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A18,全明細!$D$2:$D$975,L$4)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A18,全明細!$D$2:$D$1068,L$4)</f>
+        <v>6050</v>
       </c>
       <c r="M18" s="10" t="n">
         <f aca="false">SUM(B18:L18)</f>
-        <v>41195</v>
+        <v>47245</v>
       </c>
       <c r="N18" s="11" t="n">
         <f aca="false">IF(M$22=0,0,M18/M$22)</f>
-        <v>0.00137808168687502</v>
+        <v>0.00133327692998573</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35561,56 +38452,56 @@
         <v>105</v>
       </c>
       <c r="B19" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A19,全明細!$D$2:$D$975,B$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A19,全明細!$D$2:$D$1068,B$4)</f>
         <v>0</v>
       </c>
       <c r="C19" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A19,全明細!$D$2:$D$975,C$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A19,全明細!$D$2:$D$1068,C$4)</f>
         <v>0</v>
       </c>
       <c r="D19" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A19,全明細!$D$2:$D$975,D$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A19,全明細!$D$2:$D$1068,D$4)</f>
         <v>7756</v>
       </c>
       <c r="E19" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A19,全明細!$D$2:$D$975,E$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A19,全明細!$D$2:$D$1068,E$4)</f>
         <v>10023</v>
       </c>
       <c r="F19" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A19,全明細!$D$2:$D$975,F$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A19,全明細!$D$2:$D$1068,F$4)</f>
         <v>1375</v>
       </c>
       <c r="G19" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A19,全明細!$D$2:$D$975,G$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A19,全明細!$D$2:$D$1068,G$4)</f>
         <v>11038</v>
       </c>
       <c r="H19" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A19,全明細!$D$2:$D$975,H$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A19,全明細!$D$2:$D$1068,H$4)</f>
         <v>5215</v>
       </c>
       <c r="I19" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A19,全明細!$D$2:$D$975,I$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A19,全明細!$D$2:$D$1068,I$4)</f>
         <v>1941</v>
       </c>
       <c r="J19" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A19,全明細!$D$2:$D$975,J$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A19,全明細!$D$2:$D$1068,J$4)</f>
         <v>2558</v>
       </c>
       <c r="K19" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A19,全明細!$D$2:$D$975,K$4)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A19,全明細!$D$2:$D$1068,K$4)</f>
+        <v>5500</v>
       </c>
       <c r="L19" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A19,全明細!$D$2:$D$975,L$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A19,全明細!$D$2:$D$1068,L$4)</f>
         <v>0</v>
       </c>
       <c r="M19" s="10" t="n">
         <f aca="false">SUM(B19:L19)</f>
-        <v>39906</v>
+        <v>45406</v>
       </c>
       <c r="N19" s="11" t="n">
         <f aca="false">IF(M$22=0,0,M19/M$22)</f>
-        <v>0.00133496122821785</v>
+        <v>0.0012813794535492</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35618,118 +38509,118 @@
         <v>28</v>
       </c>
       <c r="B20" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A20,全明細!$D$2:$D$975,B$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A20,全明細!$D$2:$D$1068,B$4)</f>
         <v>0</v>
       </c>
       <c r="C20" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A20,全明細!$D$2:$D$975,C$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A20,全明細!$D$2:$D$1068,C$4)</f>
         <v>22820</v>
       </c>
       <c r="D20" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A20,全明細!$D$2:$D$975,D$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A20,全明細!$D$2:$D$1068,D$4)</f>
         <v>59370</v>
       </c>
       <c r="E20" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A20,全明細!$D$2:$D$975,E$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A20,全明細!$D$2:$D$1068,E$4)</f>
         <v>98120</v>
       </c>
       <c r="F20" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A20,全明細!$D$2:$D$975,F$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A20,全明細!$D$2:$D$1068,F$4)</f>
         <v>60073</v>
       </c>
       <c r="G20" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A20,全明細!$D$2:$D$975,G$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A20,全明細!$D$2:$D$1068,G$4)</f>
         <v>89029</v>
       </c>
       <c r="H20" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A20,全明細!$D$2:$D$975,H$4)</f>
-        <v>81829</v>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A20,全明細!$D$2:$D$1068,H$4)</f>
+        <v>89406</v>
       </c>
       <c r="I20" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A20,全明細!$D$2:$D$975,I$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A20,全明細!$D$2:$D$1068,I$4)</f>
         <v>66966</v>
       </c>
       <c r="J20" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A20,全明細!$D$2:$D$975,J$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A20,全明細!$D$2:$D$1068,J$4)</f>
         <v>64450</v>
       </c>
       <c r="K20" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A20,全明細!$D$2:$D$975,K$4)</f>
-        <v>55000</v>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A20,全明細!$D$2:$D$1068,K$4)</f>
+        <v>131109</v>
       </c>
       <c r="L20" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A20,全明細!$D$2:$D$975,L$4)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A20,全明細!$D$2:$D$1068,L$4)</f>
+        <v>12911</v>
       </c>
       <c r="M20" s="10" t="n">
         <f aca="false">SUM(B20:L20)</f>
-        <v>597657</v>
+        <v>694254</v>
       </c>
       <c r="N20" s="11" t="n">
         <f aca="false">IF(M$22=0,0,M20/M$22)</f>
-        <v>0.0199932071060241</v>
+        <v>0.0195921863001442</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>440</v>
+        <v>477</v>
       </c>
       <c r="B21" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A21,全明細!$D$2:$D$975,B$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A21,全明細!$D$2:$D$1068,B$4)</f>
         <v>0</v>
       </c>
       <c r="C21" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A21,全明細!$D$2:$D$975,C$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A21,全明細!$D$2:$D$1068,C$4)</f>
         <v>0</v>
       </c>
       <c r="D21" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A21,全明細!$D$2:$D$975,D$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A21,全明細!$D$2:$D$1068,D$4)</f>
         <v>0</v>
       </c>
       <c r="E21" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A21,全明細!$D$2:$D$975,E$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A21,全明細!$D$2:$D$1068,E$4)</f>
         <v>0</v>
       </c>
       <c r="F21" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A21,全明細!$D$2:$D$975,F$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A21,全明細!$D$2:$D$1068,F$4)</f>
         <v>0</v>
       </c>
       <c r="G21" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A21,全明細!$D$2:$D$975,G$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A21,全明細!$D$2:$D$1068,G$4)</f>
         <v>0</v>
       </c>
       <c r="H21" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A21,全明細!$D$2:$D$975,H$4)</f>
-        <v>1350511</v>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A21,全明細!$D$2:$D$1068,H$4)</f>
+        <v>0</v>
       </c>
       <c r="I21" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A21,全明細!$D$2:$D$975,I$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A21,全明細!$D$2:$D$1068,I$4)</f>
         <v>0</v>
       </c>
       <c r="J21" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A21,全明細!$D$2:$D$975,J$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A21,全明細!$D$2:$D$1068,J$4)</f>
         <v>0</v>
       </c>
       <c r="K21" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A21,全明細!$D$2:$D$975,K$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A21,全明細!$D$2:$D$1068,K$4)</f>
         <v>0</v>
       </c>
       <c r="L21" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$F$2:$F$975,$A21,全明細!$D$2:$D$975,L$4)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$F$2:$F$1068,$A21,全明細!$D$2:$D$1068,L$4)</f>
         <v>0</v>
       </c>
       <c r="M21" s="10" t="n">
         <f aca="false">SUM(B21:L21)</f>
-        <v>1350511</v>
+        <v>0</v>
       </c>
       <c r="N21" s="11" t="n">
         <f aca="false">IF(M$22=0,0,M21/M$22)</f>
-        <v>0.045178164268073</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>446</v>
+        <v>475</v>
       </c>
       <c r="B22" s="13" t="n">
         <f aca="false">SUM(B5:B21)</f>
@@ -35769,20 +38660,20 @@
       </c>
       <c r="K22" s="13" t="n">
         <f aca="false">SUM(K5:K21)</f>
-        <v>478623</v>
+        <v>5908356</v>
       </c>
       <c r="L22" s="13" t="n">
         <f aca="false">SUM(L5:L21)</f>
-        <v>31580</v>
+        <v>144093</v>
       </c>
       <c r="M22" s="13" t="n">
         <f aca="false">SUM(M5:M21)</f>
-        <v>29893003</v>
+        <v>35435249</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="B23" s="10" t="n">
         <f aca="false">B22-B5</f>
@@ -35810,7 +38701,7 @@
       </c>
       <c r="H23" s="10" t="n">
         <f aca="false">H22-H5</f>
-        <v>2229663</v>
+        <v>1272096</v>
       </c>
       <c r="I23" s="10" t="n">
         <f aca="false">I22-I5</f>
@@ -35822,15 +38713,15 @@
       </c>
       <c r="K23" s="10" t="n">
         <f aca="false">K22-K5</f>
-        <v>478623</v>
+        <v>753458</v>
       </c>
       <c r="L23" s="10" t="n">
         <f aca="false">L22-L5</f>
-        <v>31580</v>
+        <v>144093</v>
       </c>
       <c r="M23" s="10" t="n">
         <f aca="false">M22-M5</f>
-        <v>12838817</v>
+        <v>12268598</v>
       </c>
     </row>
   </sheetData>
@@ -35858,7 +38749,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>449</v>
+        <v>479</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35866,10 +38757,10 @@
         <v>0</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>444</v>
+        <v>473</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>445</v>
+        <v>474</v>
       </c>
       <c r="D3" s="15" t="s">
         <v>9</v>
@@ -35899,7 +38790,7 @@
         <v>244</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>446</v>
+        <v>475</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35907,47 +38798,47 @@
         <v>8</v>
       </c>
       <c r="B4" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$A$2:$A$975,$A4,全明細!$D$2:$D$975,B$3)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$A$2:$A$1068,$A4,全明細!$D$2:$D$1068,B$3)</f>
         <v>19277</v>
       </c>
       <c r="C4" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$A$2:$A$975,$A4,全明細!$D$2:$D$975,C$3)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$A$2:$A$1068,$A4,全明細!$D$2:$D$1068,C$3)</f>
         <v>2017892</v>
       </c>
       <c r="D4" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$A$2:$A$975,$A4,全明細!$D$2:$D$975,D$3)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$A$2:$A$1068,$A4,全明細!$D$2:$D$1068,D$3)</f>
         <v>1300106</v>
       </c>
       <c r="E4" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$A$2:$A$975,$A4,全明細!$D$2:$D$975,E$3)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$A$2:$A$1068,$A4,全明細!$D$2:$D$1068,E$3)</f>
         <v>578540</v>
       </c>
       <c r="F4" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$A$2:$A$975,$A4,全明細!$D$2:$D$975,F$3)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$A$2:$A$1068,$A4,全明細!$D$2:$D$1068,F$3)</f>
         <v>1263204</v>
       </c>
       <c r="G4" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$A$2:$A$975,$A4,全明細!$D$2:$D$975,G$3)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$A$2:$A$1068,$A4,全明細!$D$2:$D$1068,G$3)</f>
         <v>3705295</v>
       </c>
       <c r="H4" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$A$2:$A$975,$A4,全明細!$D$2:$D$975,H$3)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$A$2:$A$1068,$A4,全明細!$D$2:$D$1068,H$3)</f>
         <v>643395</v>
       </c>
       <c r="I4" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$A$2:$A$975,$A4,全明細!$D$2:$D$975,I$3)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$A$2:$A$1068,$A4,全明細!$D$2:$D$1068,I$3)</f>
         <v>1348862</v>
       </c>
       <c r="J4" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$A$2:$A$975,$A4,全明細!$D$2:$D$975,J$3)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$A$2:$A$1068,$A4,全明細!$D$2:$D$1068,J$3)</f>
         <v>1220895</v>
       </c>
       <c r="K4" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$A$2:$A$975,$A4,全明細!$D$2:$D$975,K$3)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$A$2:$A$1068,$A4,全明細!$D$2:$D$1068,K$3)</f>
         <v>401978</v>
       </c>
       <c r="L4" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$A$2:$A$975,$A4,全明細!$D$2:$D$975,L$3)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$A$2:$A$1068,$A4,全明細!$D$2:$D$1068,L$3)</f>
         <v>31580</v>
       </c>
       <c r="M4" s="10" t="n">
@@ -35960,57 +38851,57 @@
         <v>247</v>
       </c>
       <c r="B5" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$A$2:$A$975,$A5,全明細!$D$2:$D$975,B$3)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$A$2:$A$1068,$A5,全明細!$D$2:$D$1068,B$3)</f>
         <v>0</v>
       </c>
       <c r="C5" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$A$2:$A$975,$A5,全明細!$D$2:$D$975,C$3)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$A$2:$A$1068,$A5,全明細!$D$2:$D$1068,C$3)</f>
         <v>0</v>
       </c>
       <c r="D5" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$A$2:$A$975,$A5,全明細!$D$2:$D$975,D$3)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$A$2:$A$1068,$A5,全明細!$D$2:$D$1068,D$3)</f>
         <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$A$2:$A$975,$A5,全明細!$D$2:$D$975,E$3)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$A$2:$A$1068,$A5,全明細!$D$2:$D$1068,E$3)</f>
         <v>2446735</v>
       </c>
       <c r="F5" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$A$2:$A$975,$A5,全明細!$D$2:$D$975,F$3)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$A$2:$A$1068,$A5,全明細!$D$2:$D$1068,F$3)</f>
         <v>1142258</v>
       </c>
       <c r="G5" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$A$2:$A$975,$A5,全明細!$D$2:$D$975,G$3)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$A$2:$A$1068,$A5,全明細!$D$2:$D$1068,G$3)</f>
         <v>7161421</v>
       </c>
       <c r="H5" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$A$2:$A$975,$A5,全明細!$D$2:$D$975,H$3)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$A$2:$A$1068,$A5,全明細!$D$2:$D$1068,H$3)</f>
         <v>1586268</v>
       </c>
       <c r="I5" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$A$2:$A$975,$A5,全明細!$D$2:$D$975,I$3)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$A$2:$A$1068,$A5,全明細!$D$2:$D$1068,I$3)</f>
         <v>3470153</v>
       </c>
       <c r="J5" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$A$2:$A$975,$A5,全明細!$D$2:$D$975,J$3)</f>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$A$2:$A$1068,$A5,全明細!$D$2:$D$1068,J$3)</f>
         <v>1478499</v>
       </c>
       <c r="K5" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$A$2:$A$975,$A5,全明細!$D$2:$D$975,K$3)</f>
-        <v>76645</v>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$A$2:$A$1068,$A5,全明細!$D$2:$D$1068,K$3)</f>
+        <v>5506378</v>
       </c>
       <c r="L5" s="5" t="n">
-        <f aca="false">SUMIFS(全明細!$G$2:$G$975,全明細!$A$2:$A$975,$A5,全明細!$D$2:$D$975,L$3)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(全明細!$G$2:$G$1068,全明細!$A$2:$A$1068,$A5,全明細!$D$2:$D$1068,L$3)</f>
+        <v>112513</v>
       </c>
       <c r="M5" s="10" t="n">
         <f aca="false">SUM(B5:L5)</f>
-        <v>17361979</v>
+        <v>22904225</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>446</v>
+        <v>475</v>
       </c>
       <c r="B6" s="13" t="n">
         <f aca="false">SUM(B4:B5)</f>
@@ -36050,25 +38941,25 @@
       </c>
       <c r="K6" s="13" t="n">
         <f aca="false">SUM(K4:K5)</f>
-        <v>478623</v>
+        <v>5908356</v>
       </c>
       <c r="L6" s="13" t="n">
         <f aca="false">SUM(L4:L5)</f>
-        <v>31580</v>
+        <v>144093</v>
       </c>
       <c r="M6" s="13" t="n">
         <f aca="false">SUM(M4:M5)</f>
-        <v>29893003</v>
+        <v>35435249</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>450</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>451</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>
@@ -36100,27 +38991,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>452</v>
+        <v>482</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>453</v>
+        <v>483</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>454</v>
+        <v>484</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>455</v>
+        <v>485</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>456</v>
+        <v>486</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>457</v>
+        <v>487</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>458</v>
+        <v>488</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36128,14 +39019,14 @@
         <v>114</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>440</v>
+        <v>477</v>
       </c>
       <c r="C4" s="5" t="n">
-        <f aca="false">SUMIF(全明細!$E$2:$E$975,"MLT 0570666020",全明細!$G$2:$G$975)</f>
+        <f aca="false">SUMIF(全明細!$E$2:$E$1068,"MLT 0570666020",全明細!$G$2:$G$1068)</f>
         <v>443000</v>
       </c>
       <c r="D4" s="17" t="n">
-        <f aca="false">COUNTIF(全明細!$E$2:$E$975,"MLT 0570666020")</f>
+        <f aca="false">COUNTIF(全明細!$E$2:$E$1068,"MLT 0570666020")</f>
         <v>9</v>
       </c>
       <c r="E4" s="5" t="n">
@@ -36143,7 +39034,7 @@
         <v>44300</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>459</v>
+        <v>489</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36154,11 +39045,11 @@
         <v>79</v>
       </c>
       <c r="C5" s="5" t="n">
-        <f aca="false">SUMIF(全明細!$E$2:$E$975,"アフターコールナビ",全明細!$G$2:$G$975)</f>
+        <f aca="false">SUMIF(全明細!$E$2:$E$1068,"アフターコールナビ",全明細!$G$2:$G$1068)</f>
         <v>1080516</v>
       </c>
       <c r="D5" s="17" t="n">
-        <f aca="false">COUNTIF(全明細!$E$2:$E$975,"アフターコールナビ")</f>
+        <f aca="false">COUNTIF(全明細!$E$2:$E$1068,"アフターコールナビ")</f>
         <v>9</v>
       </c>
       <c r="E5" s="5" t="n">
@@ -36166,7 +39057,7 @@
         <v>108051.6</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>460</v>
+        <v>490</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36177,11 +39068,11 @@
         <v>59</v>
       </c>
       <c r="C6" s="5" t="n">
-        <f aca="false">SUMIF(全明細!$E$2:$E$975,"PAYPAL *ADVANCE STD(ACCOUNTING)",全明細!$G$2:$G$975)</f>
+        <f aca="false">SUMIF(全明細!$E$2:$E$1068,"PAYPAL *ADVANCE STD(ACCOUNTING)",全明細!$G$2:$G$1068)</f>
         <v>497500</v>
       </c>
       <c r="D6" s="17" t="n">
-        <f aca="false">COUNTIF(全明細!$E$2:$E$975,"PAYPAL *ADVANCE STD(ACCOUNTING)")</f>
+        <f aca="false">COUNTIF(全明細!$E$2:$E$1068,"PAYPAL *ADVANCE STD(ACCOUNTING)")</f>
         <v>14</v>
       </c>
       <c r="E6" s="5" t="n">
@@ -36189,7 +39080,7 @@
         <v>49750</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>461</v>
+        <v>491</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36200,11 +39091,11 @@
         <v>182</v>
       </c>
       <c r="C7" s="5" t="n">
-        <f aca="false">SUMIF(全明細!$E$2:$E$975,"PAYPAL *NKOFFICELLC(CONSULTING)",全明細!$G$2:$G$975)</f>
+        <f aca="false">SUMIF(全明細!$E$2:$E$1068,"PAYPAL *NKOFFICELLC(CONSULTING)",全明細!$G$2:$G$1068)</f>
         <v>120000</v>
       </c>
       <c r="D7" s="17" t="n">
-        <f aca="false">COUNTIF(全明細!$E$2:$E$975,"PAYPAL *NKOFFICELLC(CONSULTING)")</f>
+        <f aca="false">COUNTIF(全明細!$E$2:$E$1068,"PAYPAL *NKOFFICELLC(CONSULTING)")</f>
         <v>4</v>
       </c>
       <c r="E7" s="5" t="n">
@@ -36212,7 +39103,7 @@
         <v>12000</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>462</v>
+        <v>492</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36220,14 +39111,14 @@
         <v>86</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>463</v>
+        <v>493</v>
       </c>
       <c r="C8" s="5" t="n">
-        <f aca="false">SUMIF(全明細!$E$2:$E$975,"バランス大家サロン",全明細!$G$2:$G$975)</f>
+        <f aca="false">SUMIF(全明細!$E$2:$E$1068,"バランス大家サロン",全明細!$G$2:$G$1068)</f>
         <v>176000</v>
       </c>
       <c r="D8" s="17" t="n">
-        <f aca="false">COUNTIF(全明細!$E$2:$E$975,"バランス大家サロン")</f>
+        <f aca="false">COUNTIF(全明細!$E$2:$E$1068,"バランス大家サロン")</f>
         <v>8</v>
       </c>
       <c r="E8" s="5" t="n">
@@ -36235,7 +39126,7 @@
         <v>17600</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>464</v>
+        <v>494</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36243,22 +39134,22 @@
         <v>290</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>463</v>
+        <v>493</v>
       </c>
       <c r="C9" s="5" t="n">
-        <f aca="false">SUMIF(全明細!$E$2:$E$975,"クラブジャイアンサロン",全明細!$G$2:$G$975)</f>
-        <v>66000</v>
+        <f aca="false">SUMIF(全明細!$E$2:$E$1068,"クラブジャイアンサロン",全明細!$G$2:$G$1068)</f>
+        <v>82500</v>
       </c>
       <c r="D9" s="17" t="n">
-        <f aca="false">COUNTIF(全明細!$E$2:$E$975,"クラブジャイアンサロン")</f>
-        <v>4</v>
+        <f aca="false">COUNTIF(全明細!$E$2:$E$1068,"クラブジャイアンサロン")</f>
+        <v>5</v>
       </c>
       <c r="E9" s="5" t="n">
         <f aca="false">IF(D9=0,0,C9/10)</f>
-        <v>6600</v>
+        <v>8250</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>465</v>
+        <v>495</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36266,14 +39157,14 @@
         <v>94</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>463</v>
+        <v>493</v>
       </c>
       <c r="C10" s="5" t="n">
-        <f aca="false">SUMIF(全明細!$E$2:$E$975,"セリック不動産投資道",全明細!$G$2:$G$975)</f>
+        <f aca="false">SUMIF(全明細!$E$2:$E$1068,"セリック不動産投資道",全明細!$G$2:$G$1068)</f>
         <v>86240</v>
       </c>
       <c r="D10" s="17" t="n">
-        <f aca="false">COUNTIF(全明細!$E$2:$E$975,"セリック不動産投資道")</f>
+        <f aca="false">COUNTIF(全明細!$E$2:$E$1068,"セリック不動産投資道")</f>
         <v>8</v>
       </c>
       <c r="E10" s="5" t="n">
@@ -36281,7 +39172,7 @@
         <v>8624</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>466</v>
+        <v>496</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36292,11 +39183,11 @@
         <v>225</v>
       </c>
       <c r="C11" s="5" t="n">
-        <f aca="false">SUMIF(全明細!$E$2:$E$975,"楽待プレミアム",全明細!$G$2:$G$975)</f>
+        <f aca="false">SUMIF(全明細!$E$2:$E$1068,"楽待プレミアム",全明細!$G$2:$G$1068)</f>
         <v>6600</v>
       </c>
       <c r="D11" s="17" t="n">
-        <f aca="false">COUNTIF(全明細!$E$2:$E$975,"楽待プレミアム")</f>
+        <f aca="false">COUNTIF(全明細!$E$2:$E$1068,"楽待プレミアム")</f>
         <v>2</v>
       </c>
       <c r="E11" s="5" t="n">
@@ -36304,7 +39195,7 @@
         <v>660</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>467</v>
+        <v>497</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36312,14 +39203,14 @@
         <v>165</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>468</v>
+        <v>498</v>
       </c>
       <c r="C12" s="5" t="n">
-        <f aca="false">SUMIF(全明細!$E$2:$E$975,"MONTHLY GO(レンタカー月額)",全明細!$G$2:$G$975)</f>
+        <f aca="false">SUMIF(全明細!$E$2:$E$1068,"MONTHLY GO(レンタカー月額)",全明細!$G$2:$G$1068)</f>
         <v>570680</v>
       </c>
       <c r="D12" s="17" t="n">
-        <f aca="false">COUNTIF(全明細!$E$2:$E$975,"MONTHLY GO(レンタカー月額)")</f>
+        <f aca="false">COUNTIF(全明細!$E$2:$E$1068,"MONTHLY GO(レンタカー月額)")</f>
         <v>2</v>
       </c>
       <c r="E12" s="5" t="n">
@@ -36327,7 +39218,7 @@
         <v>57068</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36335,14 +39226,14 @@
         <v>14</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="C13" s="5" t="n">
-        <f aca="false">SUMIF(全明細!$E$2:$E$975,"ソフトバンクM",全明細!$G$2:$G$975)</f>
+        <f aca="false">SUMIF(全明細!$E$2:$E$1068,"ソフトバンクM",全明細!$G$2:$G$1068)</f>
         <v>95328</v>
       </c>
       <c r="D13" s="17" t="n">
-        <f aca="false">COUNTIF(全明細!$E$2:$E$975,"ソフトバンクM")</f>
+        <f aca="false">COUNTIF(全明細!$E$2:$E$1068,"ソフトバンクM")</f>
         <v>42</v>
       </c>
       <c r="E13" s="5" t="n">
@@ -36350,7 +39241,7 @@
         <v>9532.8</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>471</v>
+        <v>501</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36358,14 +39249,14 @@
         <v>19</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="C14" s="5" t="n">
-        <f aca="false">SUMIF(全明細!$E$2:$E$975,"GMOとくとくBB",全明細!$G$2:$G$975)</f>
+        <f aca="false">SUMIF(全明細!$E$2:$E$1068,"GMOとくとくBB",全明細!$G$2:$G$1068)</f>
         <v>30834</v>
       </c>
       <c r="D14" s="17" t="n">
-        <f aca="false">COUNTIF(全明細!$E$2:$E$975,"GMOとくとくBB")</f>
+        <f aca="false">COUNTIF(全明細!$E$2:$E$1068,"GMOとくとくBB")</f>
         <v>6</v>
       </c>
       <c r="E14" s="5" t="n">
@@ -36373,22 +39264,22 @@
         <v>3083.4</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>472</v>
+        <v>502</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>473</v>
+        <v>503</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>474</v>
+        <v>504</v>
       </c>
       <c r="C15" s="5" t="n">
-        <f aca="false">SUMIF(全明細!$E$2:$E$975,"[BtoB]03Plus",全明細!$G$2:$G$975)+SUMIF(全明細!$E$2:$E$975,"03Plus",全明細!$G$2:$G$975)</f>
+        <f aca="false">SUMIF(全明細!$E$2:$E$1068,"[BtoB]03Plus",全明細!$G$2:$G$1068)+SUMIF(全明細!$E$2:$E$1068,"03Plus",全明細!$G$2:$G$1068)</f>
         <v>15697</v>
       </c>
       <c r="D15" s="17" t="n">
-        <f aca="false">COUNTIF(全明細!$E$2:$E$975,"[BtoB]03Plus")+COUNTIF(全明細!$E$2:$E$975,"03Plus")</f>
+        <f aca="false">COUNTIF(全明細!$E$2:$E$1068,"[BtoB]03Plus")+COUNTIF(全明細!$E$2:$E$1068,"03Plus")</f>
         <v>4</v>
       </c>
       <c r="E15" s="5" t="n">
@@ -36396,7 +39287,7 @@
         <v>1569.7</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>475</v>
+        <v>505</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36404,22 +39295,22 @@
         <v>383</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="C16" s="5" t="n">
-        <f aca="false">SUMIF(全明細!$E$2:$E$975,"ドコモご利用料金",全明細!$G$2:$G$975)</f>
-        <v>21794</v>
+        <f aca="false">SUMIF(全明細!$E$2:$E$1068,"ドコモご利用料金",全明細!$G$2:$G$1068)</f>
+        <v>24530</v>
       </c>
       <c r="D16" s="17" t="n">
-        <f aca="false">COUNTIF(全明細!$E$2:$E$975,"ドコモご利用料金")</f>
-        <v>2</v>
+        <f aca="false">COUNTIF(全明細!$E$2:$E$1068,"ドコモご利用料金")</f>
+        <v>3</v>
       </c>
       <c r="E16" s="5" t="n">
         <f aca="false">IF(D16=0,0,C16/10)</f>
-        <v>2179.4</v>
+        <v>2453</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>476</v>
+        <v>506</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36427,14 +39318,14 @@
         <v>385</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>477</v>
+        <v>507</v>
       </c>
       <c r="C17" s="5" t="n">
-        <f aca="false">SUMIF(全明細!$E$2:$E$975,"Anthropic Claude サブスク",全明細!$G$2:$G$975)</f>
+        <f aca="false">SUMIF(全明細!$E$2:$E$1068,"Anthropic Claude サブスク",全明細!$G$2:$G$1068)</f>
         <v>121024</v>
       </c>
       <c r="D17" s="17" t="n">
-        <f aca="false">COUNTIF(全明細!$E$2:$E$975,"Anthropic Claude サブスク")</f>
+        <f aca="false">COUNTIF(全明細!$E$2:$E$1068,"Anthropic Claude サブスク")</f>
         <v>5</v>
       </c>
       <c r="E17" s="5" t="n">
@@ -36442,7 +39333,7 @@
         <v>12102.4</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>478</v>
+        <v>508</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36450,14 +39341,14 @@
         <v>44</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>479</v>
+        <v>509</v>
       </c>
       <c r="C18" s="5" t="n">
-        <f aca="false">SUMIF(全明細!$E$2:$E$975,"GOOGLE ONE",全明細!$G$2:$G$975)</f>
+        <f aca="false">SUMIF(全明細!$E$2:$E$1068,"GOOGLE ONE",全明細!$G$2:$G$1068)</f>
         <v>26100</v>
       </c>
       <c r="D18" s="17" t="n">
-        <f aca="false">COUNTIF(全明細!$E$2:$E$975,"GOOGLE ONE")</f>
+        <f aca="false">COUNTIF(全明細!$E$2:$E$1068,"GOOGLE ONE")</f>
         <v>9</v>
       </c>
       <c r="E18" s="5" t="n">
@@ -36465,7 +39356,7 @@
         <v>2610</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>480</v>
+        <v>510</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36473,14 +39364,14 @@
         <v>52</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>481</v>
+        <v>511</v>
       </c>
       <c r="C19" s="5" t="n">
-        <f aca="false">SUMIF(全明細!$E$2:$E$975,"YouTube Premium",全明細!$G$2:$G$975)</f>
+        <f aca="false">SUMIF(全明細!$E$2:$E$1068,"YouTube Premium",全明細!$G$2:$G$1068)</f>
         <v>11520</v>
       </c>
       <c r="D19" s="17" t="n">
-        <f aca="false">COUNTIF(全明細!$E$2:$E$975,"YouTube Premium")</f>
+        <f aca="false">COUNTIF(全明細!$E$2:$E$1068,"YouTube Premium")</f>
         <v>9</v>
       </c>
       <c r="E19" s="5" t="n">
@@ -36488,7 +39379,7 @@
         <v>1152</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>482</v>
+        <v>512</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36496,14 +39387,14 @@
         <v>81</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>483</v>
+        <v>513</v>
       </c>
       <c r="C20" s="5" t="n">
-        <f aca="false">SUMIF(全明細!$E$2:$E$975,"アドビ",全明細!$G$2:$G$975)</f>
+        <f aca="false">SUMIF(全明細!$E$2:$E$1068,"アドビ",全明細!$G$2:$G$1068)</f>
         <v>34860</v>
       </c>
       <c r="D20" s="17" t="n">
-        <f aca="false">COUNTIF(全明細!$E$2:$E$975,"アドビ")</f>
+        <f aca="false">COUNTIF(全明細!$E$2:$E$1068,"アドビ")</f>
         <v>7</v>
       </c>
       <c r="E20" s="5" t="n">
@@ -36511,7 +39402,7 @@
         <v>3486</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>484</v>
+        <v>514</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36519,14 +39410,14 @@
         <v>53</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>485</v>
+        <v>515</v>
       </c>
       <c r="C21" s="5" t="n">
-        <f aca="false">SUMIF(全明細!$E$2:$E$975,"McAfee",全明細!$G$2:$G$975)</f>
+        <f aca="false">SUMIF(全明細!$E$2:$E$1068,"McAfee",全明細!$G$2:$G$1068)</f>
         <v>12980</v>
       </c>
       <c r="D21" s="17" t="n">
-        <f aca="false">COUNTIF(全明細!$E$2:$E$975,"McAfee")</f>
+        <f aca="false">COUNTIF(全明細!$E$2:$E$1068,"McAfee")</f>
         <v>1</v>
       </c>
       <c r="E21" s="5" t="n">
@@ -36534,7 +39425,7 @@
         <v>1298</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>486</v>
+        <v>516</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36542,14 +39433,14 @@
         <v>89</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>440</v>
+        <v>477</v>
       </c>
       <c r="C22" s="5" t="n">
-        <f aca="false">SUMIF(全明細!$E$2:$E$975,"MD(MDISM) SERVICE",全明細!$G$2:$G$975)</f>
+        <f aca="false">SUMIF(全明細!$E$2:$E$1068,"MD(MDISM) SERVICE",全明細!$G$2:$G$1068)</f>
         <v>10956</v>
       </c>
       <c r="D22" s="17" t="n">
-        <f aca="false">COUNTIF(全明細!$E$2:$E$975,"MD(MDISM) SERVICE")</f>
+        <f aca="false">COUNTIF(全明細!$E$2:$E$1068,"MD(MDISM) SERVICE")</f>
         <v>2</v>
       </c>
       <c r="E22" s="5" t="n">
@@ -36557,22 +39448,22 @@
         <v>1095.6</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>487</v>
+        <v>517</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>488</v>
+        <v>518</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>489</v>
+        <v>519</v>
       </c>
       <c r="C23" s="5" t="n">
-        <f aca="false">SUMIF(全明細!$E$2:$E$975,"Apple iTunes Store",全明細!$G$2:$G$975)+SUMIF(全明細!$E$2:$E$975,"APPLE COM BILL",全明細!$G$2:$G$975)+SUMIF(全明細!$E$2:$E$975,"アマゾンサービシーズ",全明細!$G$2:$G$975)</f>
+        <f aca="false">SUMIF(全明細!$E$2:$E$1068,"Apple iTunes Store",全明細!$G$2:$G$1068)+SUMIF(全明細!$E$2:$E$1068,"APPLE COM BILL",全明細!$G$2:$G$1068)+SUMIF(全明細!$E$2:$E$1068,"アマゾンサービシーズ",全明細!$G$2:$G$1068)</f>
         <v>88324</v>
       </c>
       <c r="D23" s="17" t="n">
-        <f aca="false">COUNTIF(全明細!$E$2:$E$975,"Apple iTunes Store")+COUNTIF(全明細!$E$2:$E$975,"APPLE COM BILL")+COUNTIF(全明細!$E$2:$E$975,"アマゾンサービシーズ")</f>
+        <f aca="false">COUNTIF(全明細!$E$2:$E$1068,"Apple iTunes Store")+COUNTIF(全明細!$E$2:$E$1068,"APPLE COM BILL")+COUNTIF(全明細!$E$2:$E$1068,"アマゾンサービシーズ")</f>
         <v>42</v>
       </c>
       <c r="E23" s="5" t="n">
@@ -36580,7 +39471,7 @@
         <v>8832.4</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>490</v>
+        <v>520</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36588,14 +39479,14 @@
         <v>239</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>491</v>
+        <v>521</v>
       </c>
       <c r="C24" s="5" t="n">
-        <f aca="false">SUMIF(全明細!$E$2:$E$975,"GOアプリ(プレミアム)",全明細!$G$2:$G$975)</f>
+        <f aca="false">SUMIF(全明細!$E$2:$E$1068,"GOアプリ(プレミアム)",全明細!$G$2:$G$1068)</f>
         <v>2500</v>
       </c>
       <c r="D24" s="17" t="n">
-        <f aca="false">COUNTIF(全明細!$E$2:$E$975,"GOアプリ(プレミアム)")</f>
+        <f aca="false">COUNTIF(全明細!$E$2:$E$1068,"GOアプリ(プレミアム)")</f>
         <v>1</v>
       </c>
       <c r="E24" s="5" t="n">
@@ -36603,7 +39494,7 @@
         <v>250</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>492</v>
+        <v>522</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36611,14 +39502,14 @@
         <v>312</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>493</v>
+        <v>523</v>
       </c>
       <c r="C25" s="5" t="n">
-        <f aca="false">SUMIF(全明細!$E$2:$E$975,"エキスパ",全明細!$G$2:$G$975)</f>
+        <f aca="false">SUMIF(全明細!$E$2:$E$1068,"エキスパ",全明細!$G$2:$G$1068)</f>
         <v>29800</v>
       </c>
       <c r="D25" s="17" t="n">
-        <f aca="false">COUNTIF(全明細!$E$2:$E$975,"エキスパ")</f>
+        <f aca="false">COUNTIF(全明細!$E$2:$E$1068,"エキスパ")</f>
         <v>1</v>
       </c>
       <c r="E25" s="5" t="n">
@@ -36626,7 +39517,7 @@
         <v>2980</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>494</v>
+        <v>524</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36634,14 +39525,14 @@
         <v>348</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>495</v>
+        <v>525</v>
       </c>
       <c r="C26" s="5" t="n">
-        <f aca="false">SUMIF(全明細!$E$2:$E$975,"弥生株式会社",全明細!$G$2:$G$975)</f>
+        <f aca="false">SUMIF(全明細!$E$2:$E$1068,"弥生株式会社",全明細!$G$2:$G$1068)</f>
         <v>74470</v>
       </c>
       <c r="D26" s="17" t="n">
-        <f aca="false">COUNTIF(全明細!$E$2:$E$975,"弥生株式会社")</f>
+        <f aca="false">COUNTIF(全明細!$E$2:$E$1068,"弥生株式会社")</f>
         <v>1</v>
       </c>
       <c r="E26" s="5" t="n">
@@ -36649,45 +39540,45 @@
         <v>7447</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>496</v>
+        <v>526</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>497</v>
+        <v>527</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>298</v>
       </c>
       <c r="C27" s="5" t="n">
-        <f aca="false">SUMIF(全明細!$E$2:$E$975,"24/7Workout",全明細!$G$2:$G$975)+SUMIF(全明細!$E$2:$E$975,"24/7Workout ONLINESHOP",全明細!$G$2:$G$975)</f>
-        <v>151096</v>
+        <f aca="false">SUMIF(全明細!$E$2:$E$1068,"24/7Workout",全明細!$G$2:$G$1068)+SUMIF(全明細!$E$2:$E$1068,"24/7Workout ONLINESHOP",全明細!$G$2:$G$1068)</f>
+        <v>324940</v>
       </c>
       <c r="D27" s="17" t="n">
-        <f aca="false">COUNTIF(全明細!$E$2:$E$975,"24/7Workout")+COUNTIF(全明細!$E$2:$E$975,"24/7Workout ONLINESHOP")</f>
-        <v>7</v>
+        <f aca="false">COUNTIF(全明細!$E$2:$E$1068,"24/7Workout")+COUNTIF(全明細!$E$2:$E$1068,"24/7Workout ONLINESHOP")</f>
+        <v>9</v>
       </c>
       <c r="E27" s="5" t="n">
         <f aca="false">IF(D27=0,0,C27/10)</f>
-        <v>15109.6</v>
+        <v>32494</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>498</v>
+        <v>528</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>499</v>
+        <v>529</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>138</v>
       </c>
       <c r="C28" s="5" t="n">
-        <f aca="false">SUMIF(全明細!$E$2:$E$975,"HEARTLIFE こころの悩み相談所",全明細!$G$2:$G$975)+SUMIF(全明細!$E$2:$E$975,"Square(HeartLife こころの悩み相談)",全明細!$G$2:$G$975)</f>
+        <f aca="false">SUMIF(全明細!$E$2:$E$1068,"HEARTLIFE こころの悩み相談所",全明細!$G$2:$G$1068)+SUMIF(全明細!$E$2:$E$1068,"Square(HeartLife こころの悩み相談)",全明細!$G$2:$G$1068)</f>
         <v>41800</v>
       </c>
       <c r="D28" s="17" t="n">
-        <f aca="false">COUNTIF(全明細!$E$2:$E$975,"HEARTLIFE こころの悩み相談所")+COUNTIF(全明細!$E$2:$E$975,"Square(HeartLife こころの悩み相談)")</f>
+        <f aca="false">COUNTIF(全明細!$E$2:$E$1068,"HEARTLIFE こころの悩み相談所")+COUNTIF(全明細!$E$2:$E$1068,"Square(HeartLife こころの悩み相談)")</f>
         <v>5</v>
       </c>
       <c r="E28" s="5" t="n">
@@ -36695,7 +39586,7 @@
         <v>4180</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>500</v>
+        <v>530</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36703,14 +39594,14 @@
         <v>130</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>501</v>
+        <v>531</v>
       </c>
       <c r="C29" s="5" t="n">
-        <f aca="false">SUMIF(全明細!$E$2:$E$975,"エクスプレス予約 年会費",全明細!$G$2:$G$975)</f>
+        <f aca="false">SUMIF(全明細!$E$2:$E$1068,"エクスプレス予約 年会費",全明細!$G$2:$G$1068)</f>
         <v>1100</v>
       </c>
       <c r="D29" s="17" t="n">
-        <f aca="false">COUNTIF(全明細!$E$2:$E$975,"エクスプレス予約 年会費")</f>
+        <f aca="false">COUNTIF(全明細!$E$2:$E$1068,"エクスプレス予約 年会費")</f>
         <v>1</v>
       </c>
       <c r="E29" s="5" t="n">
@@ -36718,7 +39609,7 @@
         <v>110</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>502</v>
+        <v>532</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36726,14 +39617,14 @@
         <v>255</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>503</v>
+        <v>533</v>
       </c>
       <c r="C30" s="5" t="n">
-        <f aca="false">SUMIF(全明細!$E$2:$E$975,"プラチナカード年会費",全明細!$G$2:$G$975)</f>
+        <f aca="false">SUMIF(全明細!$E$2:$E$1068,"プラチナカード年会費",全明細!$G$2:$G$1068)</f>
         <v>96800</v>
       </c>
       <c r="D30" s="17" t="n">
-        <f aca="false">COUNTIF(全明細!$E$2:$E$975,"プラチナカード年会費")</f>
+        <f aca="false">COUNTIF(全明細!$E$2:$E$1068,"プラチナカード年会費")</f>
         <v>1</v>
       </c>
       <c r="E30" s="5" t="n">
@@ -36741,35 +39632,35 @@
         <v>9680</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>504</v>
+        <v>534</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>505</v>
+        <v>535</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>506</v>
+        <v>536</v>
       </c>
       <c r="C31" s="5" t="n">
-        <f aca="false">SUMIF(全明細!$E$2:$E$975,"セリック不動産投資道",全明細!$G$2:$G$975)+SUMIF(全明細!$E$2:$E$975,"バランス大家サロン",全明細!$G$2:$G$975)+SUMIF(全明細!$E$2:$E$975,"クラブジャイアンサロン",全明細!$G$2:$G$975)+SUMIF(全明細!$E$2:$E$975,"楽待プレミアム",全明細!$G$2:$G$975)</f>
-        <v>334840</v>
+        <f aca="false">SUMIF(全明細!$E$2:$E$1068,"セリック不動産投資道",全明細!$G$2:$G$1068)+SUMIF(全明細!$E$2:$E$1068,"バランス大家サロン",全明細!$G$2:$G$1068)+SUMIF(全明細!$E$2:$E$1068,"クラブジャイアンサロン",全明細!$G$2:$G$1068)+SUMIF(全明細!$E$2:$E$1068,"楽待プレミアム",全明細!$G$2:$G$1068)</f>
+        <v>351340</v>
       </c>
       <c r="D31" s="17" t="n">
-        <f aca="false">COUNTIF(全明細!$E$2:$E$975,"セリック不動産投資道")+COUNTIF(全明細!$E$2:$E$975,"バランス大家サロン")+COUNTIF(全明細!$E$2:$E$975,"クラブジャイアンサロン")+COUNTIF(全明細!$E$2:$E$975,"楽待プレミアム")</f>
-        <v>22</v>
+        <f aca="false">COUNTIF(全明細!$E$2:$E$1068,"セリック不動産投資道")+COUNTIF(全明細!$E$2:$E$1068,"バランス大家サロン")+COUNTIF(全明細!$E$2:$E$1068,"クラブジャイアンサロン")+COUNTIF(全明細!$E$2:$E$1068,"楽待プレミアム")</f>
+        <v>23</v>
       </c>
       <c r="E31" s="5" t="n">
         <f aca="false">IF(D31=0,0,C31/10)</f>
-        <v>33484</v>
+        <v>35134</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>507</v>
+        <v>537</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>508</v>
+        <v>538</v>
       </c>
     </row>
   </sheetData>
@@ -36800,41 +39691,41 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>509</v>
+        <v>539</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>510</v>
+        <v>540</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>511</v>
+        <v>541</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>512</v>
+        <v>542</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>513</v>
+        <v>543</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>514</v>
+        <v>544</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>515</v>
+        <v>545</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>516</v>
+        <v>546</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>517</v>
+        <v>547</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>518</v>
+        <v>548</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>519</v>
+        <v>549</v>
       </c>
       <c r="E4" s="20" t="n">
         <v>55000</v>
@@ -36846,16 +39737,16 @@
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>516</v>
+        <v>546</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>520</v>
+        <v>550</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>521</v>
+        <v>551</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>522</v>
+        <v>552</v>
       </c>
       <c r="E5" s="20" t="n">
         <v>80000</v>
@@ -36867,16 +39758,16 @@
     </row>
     <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>516</v>
+        <v>546</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>523</v>
+        <v>553</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>524</v>
+        <v>554</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>525</v>
+        <v>555</v>
       </c>
       <c r="E6" s="20" t="n">
         <v>100000</v>
@@ -36888,16 +39779,16 @@
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>526</v>
+        <v>556</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>527</v>
+        <v>557</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>528</v>
+        <v>558</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>529</v>
+        <v>559</v>
       </c>
       <c r="E7" s="20" t="n">
         <v>28000</v>
@@ -36909,16 +39800,16 @@
     </row>
     <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>526</v>
+        <v>556</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>530</v>
+        <v>560</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>531</v>
+        <v>561</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>532</v>
+        <v>562</v>
       </c>
       <c r="E8" s="20" t="n">
         <v>12000</v>
@@ -36930,16 +39821,16 @@
     </row>
     <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>526</v>
+        <v>556</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>533</v>
+        <v>563</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>534</v>
+        <v>564</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>535</v>
+        <v>565</v>
       </c>
       <c r="E9" s="20" t="n">
         <v>20000</v>
@@ -36951,16 +39842,16 @@
     </row>
     <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>526</v>
+        <v>556</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>536</v>
+        <v>566</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>537</v>
+        <v>567</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>538</v>
+        <v>568</v>
       </c>
       <c r="E10" s="20" t="n">
         <v>12000</v>
@@ -36972,16 +39863,16 @@
     </row>
     <row r="11" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
-        <v>539</v>
+        <v>569</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>540</v>
+        <v>570</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>541</v>
+        <v>571</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>542</v>
+        <v>572</v>
       </c>
       <c r="E11" s="20" t="n">
         <v>10000</v>
@@ -36993,16 +39884,16 @@
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
-        <v>539</v>
+        <v>569</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>543</v>
+        <v>573</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>544</v>
+        <v>574</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>545</v>
+        <v>575</v>
       </c>
       <c r="E12" s="20" t="n">
         <v>8000</v>
@@ -37014,16 +39905,16 @@
     </row>
     <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>539</v>
+        <v>569</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>546</v>
+        <v>576</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>547</v>
+        <v>577</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>548</v>
+        <v>578</v>
       </c>
       <c r="E13" s="20" t="n">
         <v>0</v>
@@ -37035,37 +39926,37 @@
     </row>
     <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>539</v>
+        <v>569</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>549</v>
+        <v>579</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>550</v>
+        <v>580</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="E14" s="20" t="n">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F14" s="21" t="n">
         <f aca="false">E14*12</f>
-        <v>24000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>552</v>
+        <v>582</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>554</v>
+        <v>584</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>555</v>
+        <v>585</v>
       </c>
       <c r="E15" s="20" t="n">
         <v>0</v>
@@ -37077,25 +39968,25 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="24" t="s">
-        <v>556</v>
+        <v>586</v>
       </c>
       <c r="E16" s="25" t="n">
         <f aca="false">SUM(E4:E15)</f>
-        <v>327000</v>
+        <v>330000</v>
       </c>
       <c r="F16" s="25" t="n">
         <f aca="false">SUM(F4:F15)</f>
-        <v>3924000</v>
+        <v>3960000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>557</v>
+        <v>587</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>558</v>
+        <v>588</v>
       </c>
     </row>
   </sheetData>
